--- a/Industry data.xlsx
+++ b/Industry data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bajajbroking-my.sharepoint.com/personal/siddhant_sawant_bajajbroking_in/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="8_{B0CD8669-9272-4ACC-B102-8E0D1CAC65E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BF4FC1B-8901-4617-A2A3-02944DF78DE0}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="8_{B0CD8669-9272-4ACC-B102-8E0D1CAC65E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{470C07C4-9A64-44CF-B858-FB417C1A4E1D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{9699F740-2B94-447D-9E4B-153762A7606C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{9699F740-2B94-447D-9E4B-153762A7606C}"/>
   </bookViews>
   <sheets>
     <sheet name="Broking data" sheetId="1" r:id="rId1"/>
@@ -763,9 +763,6 @@
     <t>MF customers</t>
   </si>
   <si>
-    <t>SIF AUM</t>
-  </si>
-  <si>
     <t>SIF customers</t>
   </si>
   <si>
@@ -865,9 +862,6 @@
     <t>https://www.amfiindia.com/research-information/amfi-monthly</t>
   </si>
   <si>
-    <t>SIP Contribution</t>
-  </si>
-  <si>
     <t>https://www.amfiindia.com/mutual-fund</t>
   </si>
   <si>
@@ -977,6 +971,12 @@
   </si>
   <si>
     <t>Market Share As of 30 Sep 2026</t>
+  </si>
+  <si>
+    <t>SIF AUM (In Cr)</t>
+  </si>
+  <si>
+    <t>SIP Contribution (In Cr)</t>
   </si>
 </sst>
 </file>
@@ -10886,7 +10886,7 @@
     </row>
     <row r="10" spans="1:67" ht="23" x14ac:dyDescent="0.4">
       <c r="A10" s="43" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -13239,7 +13239,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2F2E1BA-A938-4026-BEF1-69117B3FC0AD}">
-  <dimension ref="A1:AF20"/>
+  <dimension ref="A1:AG20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -13256,9 +13256,9 @@
     <col min="32" max="32" width="8.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:33" ht="15" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -13353,13 +13353,16 @@
       <c r="AF1" s="7">
         <v>46235</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG1" s="7">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A2" s="35" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B2" s="62" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C2" s="45">
         <v>53.4</v>
@@ -13451,10 +13454,13 @@
       <c r="AF2" s="45">
         <v>87.07</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG2" s="45">
+        <v>82.64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3" s="35" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B3" s="63"/>
       <c r="C3" s="45">
@@ -13547,10 +13553,13 @@
       <c r="AF3" s="45">
         <v>39.25</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG3" s="45">
+        <v>38.89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A4" s="35" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B4" s="63"/>
       <c r="C4" s="35">
@@ -13643,10 +13652,13 @@
       <c r="AF4" s="35">
         <v>1985</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG4" s="35">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A5" s="35" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B5" s="64"/>
       <c r="C5" s="45">
@@ -13739,8 +13751,11 @@
       <c r="AF5" s="45">
         <v>28.35</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG5" s="45">
+        <v>28.62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A6" s="35"/>
       <c r="B6" s="35"/>
       <c r="C6" s="35"/>
@@ -13773,13 +13788,14 @@
       <c r="AD6" s="35"/>
       <c r="AE6" s="35"/>
       <c r="AF6" s="35"/>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG6" s="35"/>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A7" s="35" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B7" s="62" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C7" s="47" t="s">
         <v>155</v>
@@ -13827,10 +13843,11 @@
       <c r="AF7" s="57">
         <v>1075</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG7" s="57"/>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A8" s="35" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B8" s="65"/>
       <c r="C8" s="47"/>
@@ -13877,10 +13894,11 @@
       <c r="AF8" s="57">
         <v>66.400000000000006</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG8" s="57"/>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A9" s="35" t="s">
-        <v>265</v>
+        <v>302</v>
       </c>
       <c r="B9" s="63"/>
       <c r="C9" s="47">
@@ -13973,8 +13991,9 @@
       <c r="AF9" s="47">
         <v>32297</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG9" s="47"/>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A10" s="35" t="s">
         <v>229</v>
       </c>
@@ -14025,8 +14044,9 @@
       <c r="AF10" s="47">
         <v>1861652</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG10" s="47"/>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A11" s="35"/>
       <c r="B11" s="35"/>
       <c r="C11" s="35"/>
@@ -14059,8 +14079,9 @@
       <c r="AD11" s="35"/>
       <c r="AE11" s="35"/>
       <c r="AF11" s="35"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG11" s="35"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A12" s="35" t="s">
         <v>230</v>
       </c>
@@ -14095,8 +14116,9 @@
       <c r="AD12" s="35"/>
       <c r="AE12" s="35"/>
       <c r="AF12" s="35"/>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG12" s="35"/>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A13" s="35"/>
       <c r="B13" s="35"/>
       <c r="C13" s="35"/>
@@ -14129,13 +14151,14 @@
       <c r="AD13" s="35"/>
       <c r="AE13" s="35"/>
       <c r="AF13" s="35"/>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG13" s="35"/>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A14" s="35" t="s">
-        <v>231</v>
+        <v>301</v>
       </c>
       <c r="B14" s="62" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C14" s="69" t="s">
         <v>155</v>
@@ -14191,10 +14214,13 @@
       <c r="AF14" s="47">
         <v>31175.43</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG14" s="47">
+        <v>38286</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A15" s="35" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B15" s="63"/>
       <c r="C15" s="72"/>
@@ -14249,10 +14275,13 @@
       <c r="AF15" s="47">
         <v>125539</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG15" s="47">
+        <v>156483</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A16" s="35" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B16" s="63"/>
       <c r="C16" s="72"/>
@@ -14307,10 +14336,13 @@
       <c r="AF16" s="47">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG16" s="47">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A17" s="35" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B17" s="64"/>
       <c r="C17" s="75"/>
@@ -14343,8 +14375,9 @@
       <c r="AD17" s="47"/>
       <c r="AE17" s="47"/>
       <c r="AF17" s="47"/>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG17" s="47"/>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A18" s="35"/>
       <c r="B18" s="35"/>
       <c r="C18" s="35"/>
@@ -14377,10 +14410,11 @@
       <c r="AD18" s="35"/>
       <c r="AE18" s="35"/>
       <c r="AF18" s="35"/>
-    </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG18" s="35"/>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A19" s="35" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B19" s="60"/>
       <c r="C19" s="78" t="s">
@@ -14439,10 +14473,11 @@
       <c r="AF19" s="35">
         <v>16.55</v>
       </c>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG19" s="35"/>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A20" s="35" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B20" s="61"/>
       <c r="C20" s="81"/>
@@ -14499,6 +14534,7 @@
       <c r="AF20" s="35">
         <v>70.53</v>
       </c>
+      <c r="AG20" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14577,10 +14613,10 @@
         <v>46266</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" hidden="1" x14ac:dyDescent="0.4">
@@ -14832,7 +14868,7 @@
     </row>
     <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.4">
       <c r="A11" s="9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B11" s="51">
         <v>1051951</v>
@@ -15120,7 +15156,7 @@
     </row>
     <row r="20" spans="1:10" ht="15" x14ac:dyDescent="0.4">
       <c r="A20" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B20" s="51">
         <v>150011</v>
@@ -15392,7 +15428,7 @@
     </row>
     <row r="29" spans="1:10" ht="15" x14ac:dyDescent="0.4">
       <c r="A29" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B29" s="54">
         <v>67432</v>
@@ -15672,7 +15708,7 @@
     </row>
     <row r="39" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A39" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B39" s="51">
         <v>66717</v>
@@ -16148,7 +16184,7 @@
     </row>
     <row r="56" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A56" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B56" s="51">
         <v>49090</v>
@@ -16232,7 +16268,7 @@
     </row>
     <row r="59" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A59" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B59" s="51" t="s">
         <v>132</v>
@@ -16932,7 +16968,7 @@
     </row>
     <row r="84" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A84" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B84" s="51" t="s">
         <v>155</v>
@@ -17408,7 +17444,7 @@
     </row>
     <row r="101" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A101" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B101" s="51" t="s">
         <v>155</v>
@@ -17436,7 +17472,7 @@
     </row>
     <row r="102" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A102" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B102" s="51" t="s">
         <v>155</v>
@@ -17520,7 +17556,7 @@
     </row>
     <row r="105" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A105" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B105" s="51" t="s">
         <v>155</v>
@@ -17632,7 +17668,7 @@
     </row>
     <row r="109" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A109" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B109" s="51" t="s">
         <v>155</v>
@@ -18052,7 +18088,7 @@
     </row>
     <row r="124" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A124" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B124" s="51" t="s">
         <v>155</v>
@@ -18136,7 +18172,7 @@
     </row>
     <row r="127" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A127" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B127" s="51" t="s">
         <v>155</v>
@@ -18360,7 +18396,7 @@
     </row>
     <row r="135" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A135" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B135" s="51" t="s">
         <v>155</v>
@@ -18612,7 +18648,7 @@
     </row>
     <row r="144" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A144" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B144" s="51" t="s">
         <v>132</v>
@@ -18976,7 +19012,7 @@
     </row>
     <row r="157" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A157" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B157" s="51" t="s">
         <v>155</v>
@@ -19343,7 +19379,7 @@
     </row>
     <row r="170" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A170" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B170" s="51" t="s">
         <v>155</v>
@@ -19824,7 +19860,7 @@
     </row>
     <row r="187" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A187" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B187" s="51" t="s">
         <v>155</v>
@@ -20783,7 +20819,7 @@
     </row>
     <row r="221" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A221" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B221" s="51" t="s">
         <v>155</v>
@@ -20810,7 +20846,7 @@
     </row>
     <row r="222" spans="1:8" ht="15" x14ac:dyDescent="0.4">
       <c r="A222" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B222" s="51" t="s">
         <v>155</v>
@@ -20994,13 +21030,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="59" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1" s="59" t="s">
+        <v>268</v>
+      </c>
+      <c r="C1" s="59" t="s">
         <v>269</v>
-      </c>
-      <c r="B1" s="59" t="s">
-        <v>270</v>
-      </c>
-      <c r="C1" s="59" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.35">
@@ -21008,10 +21044,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="58" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -21019,10 +21055,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -21030,10 +21066,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -21044,7 +21080,7 @@
         <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -21052,10 +21088,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -21063,10 +21099,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -21074,10 +21110,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -21085,10 +21121,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C9" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -21096,10 +21132,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -21107,10 +21143,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C11" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -21118,10 +21154,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -21129,10 +21165,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C13" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -21140,10 +21176,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C14" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -21151,10 +21187,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -21162,10 +21198,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C16" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>

--- a/Industry data.xlsx
+++ b/Industry data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bajajbroking-my.sharepoint.com/personal/siddhant_sawant_bajajbroking_in/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="142" documentId="8_{B0CD8669-9272-4ACC-B102-8E0D1CAC65E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AA722BE-CE4F-46BA-A218-0FDC7C53B5CF}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="8_{B0CD8669-9272-4ACC-B102-8E0D1CAC65E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF766402-6112-4BAE-A21E-AC76FC1C541A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{9699F740-2B94-447D-9E4B-153762A7606C}"/>
   </bookViews>
@@ -2438,7 +2438,7 @@
         </row>
         <row r="25">
           <cell r="B25" t="str">
-            <v>Nu Investors Technologies Private Limited (lemonn)</v>
+            <v>Nu Investors Technologies Private Limited</v>
           </cell>
           <cell r="C25" t="str">
             <v>No</v>
@@ -2728,7 +2728,7 @@
         </row>
         <row r="35">
           <cell r="B35" t="str">
-            <v>Moneywise Finvest Limited (Stoxkart)</v>
+            <v>Moneywise Finvest Limited</v>
           </cell>
           <cell r="C35" t="str">
             <v>No</v>
@@ -3047,7 +3047,7 @@
         </row>
         <row r="46">
           <cell r="B46" t="str">
-            <v>Aaritya Broking Private Ltd (Sahi)</v>
+            <v>Aaritya Broking Private Ltd</v>
           </cell>
           <cell r="C46" t="str">
             <v>No</v>
@@ -3076,7 +3076,7 @@
         </row>
         <row r="47">
           <cell r="B47" t="str">
-            <v>Indusind Securities (Reliance Securities Limited)</v>
+            <v>Indusind Securities Limited (formerly Known As Reliance Securities Limited)</v>
           </cell>
           <cell r="C47" t="str">
             <v>No</v>
@@ -4439,7 +4439,7 @@
         </row>
         <row r="94">
           <cell r="B94" t="str">
-            <v>South Asian Stocks Ltd. (incredstocko.in)</v>
+            <v>South Asian Stocks Ltd.</v>
           </cell>
           <cell r="C94" t="str">
             <v>No</v>
@@ -15210,7 +15210,6 @@
         <v>252951</v>
       </c>
       <c r="G20" s="49">
-        <f>VLOOKUP(TRIM(A20),[1]isc_report1C_2627_300926!$B$10:$J$272,9,FALSE)</f>
         <v>281028</v>
       </c>
       <c r="H20" s="58">
@@ -15482,7 +15481,6 @@
         <v>134637</v>
       </c>
       <c r="G29" s="49">
-        <f>VLOOKUP(TRIM(A29),[1]isc_report1C_2627_300926!$B$10:$J$272,9,FALSE)</f>
         <v>152255</v>
       </c>
       <c r="H29" s="58">
@@ -15762,7 +15760,6 @@
         <v>80710</v>
       </c>
       <c r="G39" s="49">
-        <f>VLOOKUP(TRIM(A39),[1]isc_report1C_2627_300926!$B$10:$J$272,9,FALSE)</f>
         <v>81373</v>
       </c>
       <c r="H39" s="58">
@@ -16238,7 +16235,6 @@
         <v>48869</v>
       </c>
       <c r="G56" s="49">
-        <f>VLOOKUP(TRIM(A56),[1]isc_report1C_2627_300926!$B$10:$J$272,9,FALSE)</f>
         <v>48610</v>
       </c>
       <c r="H56" s="58">
@@ -16322,7 +16318,6 @@
         <v>41057</v>
       </c>
       <c r="G59" s="49">
-        <f>VLOOKUP(TRIM(A59),[1]isc_report1C_2627_300926!$B$10:$J$272,9,FALSE)</f>
         <v>44365</v>
       </c>
       <c r="H59" s="58">
@@ -20430,7 +20425,6 @@
         <v>44925108</v>
       </c>
       <c r="G206" s="60">
-        <f>SUM(G4:G201)</f>
         <v>45080318</v>
       </c>
       <c r="H206" s="35"/>

--- a/Industry data.xlsx
+++ b/Industry data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bajajbroking-my.sharepoint.com/personal/siddhant_sawant_bajajbroking_in/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\siddhantsawant\Downloads\Strategy Tool\competitor-benchmark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="8_{B0CD8669-9272-4ACC-B102-8E0D1CAC65E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF766402-6112-4BAE-A21E-AC76FC1C541A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC59049-1129-4BEE-884A-89DFD225B374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{9699F740-2B94-447D-9E4B-153762A7606C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{9699F740-2B94-447D-9E4B-153762A7606C}"/>
   </bookViews>
   <sheets>
     <sheet name="Broking data" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NSE active client data'!$A$2:$J$2</definedName>
@@ -68,8 +69,32 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={5A1865E8-B5F1-4437-BB1E-C4BC5624C76F}</author>
+  </authors>
+  <commentList>
+    <comment ref="L16" authorId="0" shapeId="0" xr:uid="{5A1865E8-B5F1-4437-BB1E-C4BC5624C76F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+[Tasks]
+There is a task anchored to this comment that cannot be viewed in your client.
+Comment:
+    @Siddhant Sawant 3% kaa se aaya. Also sae tat note forbakup.
+Reply:
+    It will come in others, had not completed it. Now did it and yes will add that note for backup
+Reply:
+    Ok thanks</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="333">
   <si>
     <t>Source</t>
   </si>
@@ -980,32 +1005,102 @@
     <t>SIP AUM (In Cr)</t>
   </si>
   <si>
-    <t>Company</t>
-  </si>
-  <si>
     <t>Groww</t>
   </si>
   <si>
-    <t>ROCE</t>
-  </si>
-  <si>
     <t>ROE</t>
   </si>
   <si>
-    <t>CATEGORY</t>
-  </si>
-  <si>
-    <t>Tech-Drive</t>
-  </si>
-  <si>
     <t>Zerodha</t>
+  </si>
+  <si>
+    <t>FY26</t>
+  </si>
+  <si>
+    <t>Tech Driven Brokers</t>
+  </si>
+  <si>
+    <t>Traditional Brokers</t>
+  </si>
+  <si>
+    <t>Angel One</t>
+  </si>
+  <si>
+    <t>Bajaj Broking</t>
+  </si>
+  <si>
+    <t>Motilal</t>
+  </si>
+  <si>
+    <t>ICICI Sec</t>
+  </si>
+  <si>
+    <t>HDFC Sec</t>
+  </si>
+  <si>
+    <t>Kotak Sec</t>
+  </si>
+  <si>
+    <t>Total Revenue</t>
+  </si>
+  <si>
+    <t>PAT</t>
+  </si>
+  <si>
+    <t>opening networth</t>
+  </si>
+  <si>
+    <t>Networth</t>
+  </si>
+  <si>
+    <t>closing net worth</t>
+  </si>
+  <si>
+    <t>Avg Networth</t>
+  </si>
+  <si>
+    <t>MTF book</t>
+  </si>
+  <si>
+    <t>Revenue Mix</t>
+  </si>
+  <si>
+    <t>Equity Derivatives (F&amp;O)</t>
+  </si>
+  <si>
+    <t>Broking</t>
+  </si>
+  <si>
+    <t>Stocks (Cash)</t>
+  </si>
+  <si>
+    <t>Commodity Derivatives</t>
+  </si>
+  <si>
+    <t>Distribution/Services</t>
+  </si>
+  <si>
+    <t>MTF</t>
+  </si>
+  <si>
+    <t>MTF/Loan Interest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTF </t>
+  </si>
+  <si>
+    <t>DPC</t>
+  </si>
+  <si>
+    <t>Treasury/Interest Income</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="9">
+  <numFmts count="12">
+    <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -1015,8 +1110,10 @@
     <numFmt numFmtId="169" formatCode="0.0"/>
     <numFmt numFmtId="170" formatCode="[$-409]d/mmm/yy;@"/>
     <numFmt numFmtId="171" formatCode="[&gt;=10000000]#.###\,##\,##0;[&gt;=100000]#.###\,##0;##,##0.0"/>
+    <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="173" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1157,8 +1254,42 @@
       <color indexed="8"/>
       <name val="Rubik"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1204,6 +1335,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1386,7 +1523,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="161">
+  <cellStyleXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1550,8 +1687,9 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1762,8 +1900,120 @@
     <xf numFmtId="4" fontId="20" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="161" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="161" applyFont="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="161">
+  <cellStyles count="162">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Comma 10 5" xfId="15" xr:uid="{537EED21-785E-48F4-A453-1417CCF62D6D}"/>
     <cellStyle name="Comma 11" xfId="51" xr:uid="{A31B6CD8-098C-4A8D-8D4E-4D6DF514FDB7}"/>
@@ -1878,6 +2128,7 @@
     <cellStyle name="Comma 7 2 4" xfId="152" xr:uid="{9FF2F0B4-7B2F-4039-9F35-03DCC0ED245C}"/>
     <cellStyle name="Comma 8" xfId="99" xr:uid="{05A2EC26-EF02-4F86-B073-404B8641F454}"/>
     <cellStyle name="Comma 9" xfId="142" xr:uid="{DA66A303-E542-4D22-9E64-FAF6256258B8}"/>
+    <cellStyle name="Currency" xfId="161" builtinId="4"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Indian Comma" xfId="25" xr:uid="{6EC22827-C830-4F05-B830-B1D9CA67E242}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1990,11 +2241,45 @@
 </styleSheet>
 </file>
 
+<file path=xl/documenttasks/documenttask1.xml><?xml version="1.0" encoding="utf-8"?>
+<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
+  <Task id="{DCC9742B-ADF0-42D1-8289-62D924E166AA}">
+    <Anchor>
+      <Comment id="{5A1865E8-B5F1-4437-BB1E-C4BC5624C76F}"/>
+    </Anchor>
+    <History>
+      <Event time="2026-10-21T11:25:37.90" id="{B173F471-2C3F-4BA8-915B-7CFCFD43D415}">
+        <Attribution userId="S::prabal.selwadiya@bajajbroking.in::ba547732-48f4-4194-8b68-ec3df1128f3a" userName="Prabal Selwadiya" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{5A1865E8-B5F1-4437-BB1E-C4BC5624C76F}"/>
+        </Anchor>
+        <Create/>
+      </Event>
+      <Event time="2026-10-21T11:25:37.90" id="{8B4513C8-AB87-4B4B-B921-B9C365CCED43}">
+        <Attribution userId="S::prabal.selwadiya@bajajbroking.in::ba547732-48f4-4194-8b68-ec3df1128f3a" userName="Prabal Selwadiya" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{5A1865E8-B5F1-4437-BB1E-C4BC5624C76F}"/>
+        </Anchor>
+        <Assign userId="S::siddhant.sawant@bajajbroking.in::705fb5c3-f8e0-4b2a-9b15-78f09f936f1f" userName="Siddhant Sawant" userProvider="AD"/>
+      </Event>
+      <Event time="2026-10-21T11:25:37.90" id="{481C59A6-CD19-4888-BFEB-7154DF0A1DEB}">
+        <Attribution userId="S::prabal.selwadiya@bajajbroking.in::ba547732-48f4-4194-8b68-ec3df1128f3a" userName="Prabal Selwadiya" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{5A1865E8-B5F1-4437-BB1E-C4BC5624C76F}"/>
+        </Anchor>
+        <SetTitle title="@Siddhant Sawant 3% kaa se aaya. Also sae tat note forbakup."/>
+      </Event>
+    </History>
+  </Task>
+</Tasks>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="isc_report1C_2627_300926"/>
@@ -9634,8 +9919,52 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Consol"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="6">
+          <cell r="S6">
+            <v>5907.8440733620082</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="S32">
+            <v>0.15717022338137798</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="S51">
+            <v>842.84570941674997</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="S52">
+            <v>778.12631234324999</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="S53">
+            <v>271.37660286208001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Siddhant Sawant" id="{13F8032C-99AB-4D98-B2AF-EA5A9143ECF7}" userId="siddhant.sawant@bajajbroking.in" providerId="PeoplePicker"/>
+  <person displayName="Siddhant Sawant" id="{8C3F3FE3-0318-45BA-87B6-CF039B3E0264}" userId="S::siddhant.sawant@bajajbroking.in::705fb5c3-f8e0-4b2a-9b15-78f09f936f1f" providerId="AD"/>
   <person displayName="Prabal Selwadiya" id="{45E6C18B-D63D-45C7-B049-27FAB2BD2D7A}" userId="S::prabal.selwadiya@bajajbroking.in::ba547732-48f4-4194-8b68-ec3df1128f3a" providerId="AD"/>
 </personList>
 </file>
@@ -9964,6 +10293,23 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="L16" dT="2026-10-21T11:25:37.91" personId="{45E6C18B-D63D-45C7-B049-27FAB2BD2D7A}" id="{5A1865E8-B5F1-4437-BB1E-C4BC5624C76F}">
+    <text>@Siddhant Sawant 3% kaa se aaya. Also sae tat note forbakup.</text>
+    <mentions>
+      <mention mentionpersonId="{13F8032C-99AB-4D98-B2AF-EA5A9143ECF7}" mentionId="{D5684F4C-CE30-48F2-81DA-90710F47F32B}" startIndex="0" length="16"/>
+    </mentions>
+  </threadedComment>
+  <threadedComment ref="L16" dT="2026-10-21T11:34:53.33" personId="{8C3F3FE3-0318-45BA-87B6-CF039B3E0264}" id="{E6D4EE95-46E7-4D47-B525-F1CECFF2106A}" parentId="{5A1865E8-B5F1-4437-BB1E-C4BC5624C76F}">
+    <text>It will come in others, had not completed it. Now did it and yes will add that note for backup</text>
+  </threadedComment>
+  <threadedComment ref="L16" dT="2026-10-21T13:05:03.34" personId="{45E6C18B-D63D-45C7-B049-27FAB2BD2D7A}" id="{534711B7-95D5-416A-BB04-8458892A758D}" parentId="{5A1865E8-B5F1-4437-BB1E-C4BC5624C76F}">
+    <text>Ok thanks</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EFFFC54-6ABB-4788-81D8-C6029B6E6988}">
   <dimension ref="A1:BO40"/>
@@ -20704,48 +21050,774 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B550A9BB-8240-4E8C-9C06-0026F4160F53}">
-  <dimension ref="A1:D3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B550A9BB-8240-4E8C-9C06-0026F4160F53}">
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" customWidth="1"/>
+    <col min="3" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.81640625" customWidth="1"/>
+    <col min="8" max="8" width="15.81640625" customWidth="1"/>
+    <col min="9" max="9" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="96" t="s">
+        <v>306</v>
+      </c>
+      <c r="B1" s="96"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C2" s="97" t="s">
         <v>307</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D2" s="97"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="J2" s="97" t="s">
+        <v>308</v>
+      </c>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C3" s="99" t="s">
         <v>303</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D3" s="99" t="s">
+        <v>309</v>
+      </c>
+      <c r="E3" s="99" t="s">
         <v>305</v>
       </c>
-      <c r="D1" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="F3" s="99" t="s">
+        <v>310</v>
+      </c>
+      <c r="G3" s="100"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="99" t="s">
+        <v>311</v>
+      </c>
+      <c r="J3" s="99" t="s">
+        <v>312</v>
+      </c>
+      <c r="K3" s="99" t="s">
+        <v>313</v>
+      </c>
+      <c r="L3" s="99" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="102" t="s">
+        <v>315</v>
+      </c>
+      <c r="C4" s="103">
+        <v>4644.5</v>
+      </c>
+      <c r="D4" s="104">
+        <v>5072</v>
+      </c>
+      <c r="E4" s="103">
+        <v>7464</v>
+      </c>
+      <c r="F4" s="104">
+        <v>1069.6300000000001</v>
+      </c>
+      <c r="G4" s="104"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="103">
+        <v>4890</v>
+      </c>
+      <c r="J4" s="103">
+        <v>5889.8</v>
+      </c>
+      <c r="K4" s="103">
+        <v>3110.15</v>
+      </c>
+      <c r="L4" s="103">
+        <f>546149.37/100</f>
+        <v>5461.4937</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A5" s="102" t="s">
+        <v>316</v>
+      </c>
+      <c r="C5" s="103">
+        <v>2083</v>
+      </c>
+      <c r="D5" s="104">
+        <v>1022.7</v>
+      </c>
+      <c r="E5" s="103">
+        <v>4283</v>
+      </c>
+      <c r="F5" s="104">
+        <v>202.57</v>
+      </c>
+      <c r="G5" s="104"/>
+      <c r="I5" s="103">
+        <v>922.51</v>
+      </c>
+      <c r="J5" s="103">
+        <v>1713.1</v>
+      </c>
+      <c r="K5" s="103">
+        <v>929.99400000000003</v>
+      </c>
+      <c r="L5" s="103">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="102" t="s">
+        <v>317</v>
+      </c>
+      <c r="C6" s="103">
+        <f>48554.45/10</f>
+        <v>4855.4449999999997</v>
+      </c>
+      <c r="D6" s="104">
+        <f>(55075.74+903)/10</f>
+        <v>5597.8739999999998</v>
+      </c>
+      <c r="E6" s="106">
+        <v>16500</v>
+      </c>
+      <c r="F6" s="104">
+        <v>1288.93</v>
+      </c>
+      <c r="G6" s="104"/>
+      <c r="I6" s="103">
+        <f>711687/100</f>
+        <v>7116.87</v>
+      </c>
+      <c r="J6" s="103">
+        <f>54220.6/10</f>
+        <v>5422.0599999999995</v>
+      </c>
+      <c r="K6" s="103">
+        <v>3348.59</v>
+      </c>
+      <c r="L6" s="103">
+        <f>1000868.33/100</f>
+        <v>10008.683299999999</v>
+      </c>
+      <c r="P6">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="102" t="s">
+        <v>318</v>
+      </c>
+      <c r="B7" s="107" t="s">
+        <v>319</v>
+      </c>
+      <c r="C7" s="103">
+        <v>9651.4000000000015</v>
+      </c>
+      <c r="D7" s="104">
+        <v>6201.9</v>
+      </c>
+      <c r="E7" s="103">
+        <f>E6+E5</f>
+        <v>20783</v>
+      </c>
+      <c r="F7" s="104">
+        <v>2085.9699999999998</v>
+      </c>
+      <c r="G7" s="104"/>
+      <c r="I7" s="103">
+        <v>7950.56</v>
+      </c>
+      <c r="J7" s="103">
+        <v>6294.5</v>
+      </c>
+      <c r="K7" s="103">
+        <v>3595.92</v>
+      </c>
+      <c r="L7" s="103">
+        <v>11614.4</v>
+      </c>
+      <c r="P7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A8" s="102" t="s">
+        <v>320</v>
+      </c>
+      <c r="B8" s="107"/>
+      <c r="C8" s="103">
+        <f>AVERAGE(C6:C7)</f>
+        <v>7253.4225000000006</v>
+      </c>
+      <c r="D8" s="103">
+        <f t="shared" ref="D8:L8" si="0">AVERAGE(D6:D7)</f>
+        <v>5899.8869999999997</v>
+      </c>
+      <c r="E8" s="103">
+        <f t="shared" si="0"/>
+        <v>18641.5</v>
+      </c>
+      <c r="F8" s="103">
+        <v>1687.45</v>
+      </c>
+      <c r="G8" s="104"/>
+      <c r="H8" s="104"/>
+      <c r="I8" s="103">
+        <f t="shared" si="0"/>
+        <v>7533.7150000000001</v>
+      </c>
+      <c r="J8" s="103">
+        <f t="shared" si="0"/>
+        <v>5858.28</v>
+      </c>
+      <c r="K8" s="103">
+        <f t="shared" si="0"/>
+        <v>3472.2550000000001</v>
+      </c>
+      <c r="L8" s="103">
+        <f t="shared" si="0"/>
+        <v>10811.541649999999</v>
+      </c>
+      <c r="P8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9" s="102" t="s">
         <v>304</v>
       </c>
-      <c r="C2" s="62">
-        <v>0.373</v>
-      </c>
-      <c r="D2" s="62">
-        <v>0.28799999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
+      <c r="C9" s="108">
+        <f>C5/AVERAGE(C6,C7)</f>
+        <v>0.28717477852696432</v>
+      </c>
+      <c r="D9" s="109">
+        <f>D5/AVERAGE(D6:D7)</f>
+        <v>0.17334230299665063</v>
+      </c>
+      <c r="E9" s="108">
+        <f>E5/AVERAGE(E6:E7)</f>
+        <v>0.22975618914786899</v>
+      </c>
+      <c r="F9" s="108">
+        <f>F5/AVERAGE(F6:F7)</f>
+        <v>0.12004503837150732</v>
+      </c>
+      <c r="G9" s="110"/>
+      <c r="I9" s="108">
+        <f>I5/AVERAGE(I6:I7)</f>
+        <v>0.12245087582952102</v>
+      </c>
+      <c r="J9" s="108">
+        <f>J5/AVERAGE(J6:J7)</f>
+        <v>0.29242371481049045</v>
+      </c>
+      <c r="K9" s="108">
+        <f>K5/AVERAGE(K6:K7)</f>
+        <v>0.2678357436305801</v>
+      </c>
+      <c r="L9" s="108">
+        <f>L5/AVERAGE(L6:L7)</f>
+        <v>0.15390959530734455</v>
+      </c>
+      <c r="P9">
+        <f>P6-P7-P8</f>
+        <v>831</v>
+      </c>
+      <c r="Q9" s="105">
+        <f>P9/P6</f>
+        <v>0.79218303145853197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10" s="102" t="s">
+        <v>321</v>
+      </c>
+      <c r="C10" s="103">
+        <v>2814.2</v>
+      </c>
+      <c r="D10" s="104">
+        <v>5128</v>
+      </c>
+      <c r="E10" s="106">
+        <v>7000</v>
+      </c>
+      <c r="F10" s="111">
+        <v>7985</v>
+      </c>
+      <c r="I10" s="103">
+        <v>5767.36</v>
+      </c>
+      <c r="J10" s="103">
+        <v>14561.34</v>
+      </c>
+      <c r="K10" s="103">
+        <v>7132.66</v>
+      </c>
+      <c r="L10" s="103">
+        <v>13363.15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O11" s="104"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B12" s="35"/>
+      <c r="C12" s="112" t="s">
+        <v>303</v>
+      </c>
+      <c r="D12" s="112" t="s">
         <v>309</v>
       </c>
+      <c r="E12" s="112" t="s">
+        <v>305</v>
+      </c>
+      <c r="F12" s="99" t="s">
+        <v>310</v>
+      </c>
+      <c r="G12" s="100"/>
+      <c r="H12" s="101"/>
+      <c r="I12" s="99" t="s">
+        <v>311</v>
+      </c>
+      <c r="J12" s="99" t="s">
+        <v>312</v>
+      </c>
+      <c r="K12" s="99" t="s">
+        <v>313</v>
+      </c>
+      <c r="L12" s="99" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A13" s="113" t="s">
+        <v>322</v>
+      </c>
+      <c r="B13" s="114" t="s">
+        <v>323</v>
+      </c>
+      <c r="C13" s="115">
+        <v>0.55120000000000002</v>
+      </c>
+      <c r="D13" s="116">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="E13" s="117">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="F13" s="50">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="G13" s="50"/>
+      <c r="H13" s="118" t="s">
+        <v>324</v>
+      </c>
+      <c r="I13" s="119">
+        <f t="shared" ref="I13:I19" si="1">P13/$I$4</f>
+        <v>0.15912603524401842</v>
+      </c>
+      <c r="J13" s="120">
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="K13" s="120">
+        <f>1012/K4</f>
+        <v>0.32538623539057598</v>
+      </c>
+      <c r="L13" s="120">
+        <v>0.44</v>
+      </c>
+      <c r="M13" s="121"/>
+      <c r="P13" s="39">
+        <f>[2]Consol!$S$52</f>
+        <v>778.12631234324999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A14" s="113"/>
+      <c r="B14" s="114" t="s">
+        <v>325</v>
+      </c>
+      <c r="C14" s="115">
+        <v>0.17780000000000001</v>
+      </c>
+      <c r="D14" s="116">
+        <v>8.2500000000000004E-2</v>
+      </c>
+      <c r="E14" s="117"/>
+      <c r="F14" s="50">
+        <v>7.9699999999999993E-2</v>
+      </c>
+      <c r="G14" s="50"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="119">
+        <f t="shared" si="1"/>
+        <v>0.17236108577029652</v>
+      </c>
+      <c r="J14" s="120"/>
+      <c r="K14" s="120"/>
+      <c r="L14" s="120"/>
+      <c r="N14" s="109"/>
+      <c r="P14" s="39">
+        <f>[2]Consol!$S$51</f>
+        <v>842.84570941674997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A15" s="113"/>
+      <c r="B15" s="114" t="s">
+        <v>326</v>
+      </c>
+      <c r="C15" s="115">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="D15" s="122">
+        <v>0.06</v>
+      </c>
+      <c r="E15" s="117"/>
+      <c r="F15" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="G15" s="50"/>
+      <c r="H15" s="118"/>
+      <c r="I15" s="119">
+        <f t="shared" si="1"/>
+        <v>5.5496237804106341E-2</v>
+      </c>
+      <c r="J15" s="120"/>
+      <c r="K15" s="120"/>
+      <c r="L15" s="120"/>
+      <c r="M15" s="104"/>
+      <c r="P15" s="39">
+        <f>[2]Consol!$S$53</f>
+        <v>271.37660286208001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="113"/>
+      <c r="B16" s="114" t="s">
+        <v>327</v>
+      </c>
+      <c r="C16" s="115" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" s="116">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="E16" s="123" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="G16" s="50"/>
+      <c r="H16" s="124" t="s">
+        <v>327</v>
+      </c>
+      <c r="I16" s="119">
+        <f t="shared" si="1"/>
+        <v>0.18988490239522635</v>
+      </c>
+      <c r="J16" s="119">
+        <f>1100/J4</f>
+        <v>0.18676355733641209</v>
+      </c>
+      <c r="K16" s="119">
+        <f>487/K4</f>
+        <v>0.15658408758420012</v>
+      </c>
+      <c r="L16" s="119" t="s">
+        <v>132</v>
+      </c>
+      <c r="M16" s="104"/>
+      <c r="P16" s="39">
+        <f>[2]Consol!$S$32*[2]Consol!$S$6</f>
+        <v>928.5371727126568</v>
+      </c>
+      <c r="Q16" s="105">
+        <f>P16/5000</f>
+        <v>0.18570743454253136</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="113"/>
+      <c r="B17" s="114" t="s">
+        <v>328</v>
+      </c>
+      <c r="C17" s="115">
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="D17" s="125">
+        <f>840/D4</f>
+        <v>0.16561514195583596</v>
+      </c>
+      <c r="E17" s="126">
+        <f>448/E4</f>
+        <v>6.0021436227224008E-2</v>
+      </c>
+      <c r="F17" s="50">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="G17" s="50"/>
+      <c r="H17" s="124" t="s">
+        <v>329</v>
+      </c>
+      <c r="I17" s="119">
+        <f t="shared" si="1"/>
+        <v>0.16012269938650306</v>
+      </c>
+      <c r="J17" s="119">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="K17" s="119">
+        <f>912.55/K4</f>
+        <v>0.29341028567753963</v>
+      </c>
+      <c r="L17" s="127">
+        <v>0.26</v>
+      </c>
+      <c r="M17" s="128"/>
+      <c r="P17">
+        <f>783</f>
+        <v>783</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A18" s="113"/>
+      <c r="B18" s="114" t="s">
+        <v>331</v>
+      </c>
+      <c r="C18" s="129" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="130"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="50">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="G18" s="50"/>
+      <c r="H18" s="124" t="s">
+        <v>331</v>
+      </c>
+      <c r="I18" s="119">
+        <f t="shared" si="1"/>
+        <v>6.0531697341513292E-2</v>
+      </c>
+      <c r="J18" s="119" t="s">
+        <v>132</v>
+      </c>
+      <c r="K18" s="119">
+        <f>45/K4</f>
+        <v>1.4468755526260792E-2</v>
+      </c>
+      <c r="L18" s="131" t="s">
+        <v>132</v>
+      </c>
+      <c r="M18" s="128"/>
+      <c r="P18">
+        <v>296</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="113"/>
+      <c r="B19" s="132" t="s">
+        <v>332</v>
+      </c>
+      <c r="C19" s="129">
+        <v>0.1143</v>
+      </c>
+      <c r="D19" s="133">
+        <f>(1619-840)/D4</f>
+        <v>0.15358832807570977</v>
+      </c>
+      <c r="E19" s="134">
+        <f>2269/E4</f>
+        <v>0.30399249732047162</v>
+      </c>
+      <c r="F19" s="50">
+        <v>0.1011</v>
+      </c>
+      <c r="H19" s="124" t="s">
+        <v>332</v>
+      </c>
+      <c r="I19" s="119">
+        <f t="shared" si="1"/>
+        <v>0.10777096114519427</v>
+      </c>
+      <c r="J19" s="119">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K19" s="119">
+        <f>585.38/K4-K18</f>
+        <v>0.17374724691735124</v>
+      </c>
+      <c r="L19" s="119">
+        <v>0.21</v>
+      </c>
+      <c r="M19" s="121"/>
+      <c r="P19">
+        <f>1606-P17-P18</f>
+        <v>527</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A20" s="113"/>
+      <c r="B20" s="114" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" s="115">
+        <v>6.6100000000000006E-2</v>
+      </c>
+      <c r="D20" s="122">
+        <f>1-SUM(D13:D19)</f>
+        <v>4.6296529968454347E-2</v>
+      </c>
+      <c r="E20" s="135">
+        <f>1-SUM(E13:E19)</f>
+        <v>0.26898606645230438</v>
+      </c>
+      <c r="F20" s="50">
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="G20" s="50"/>
+      <c r="H20" s="124" t="s">
+        <v>208</v>
+      </c>
+      <c r="I20" s="136">
+        <f>1-SUM(I13:I19)</f>
+        <v>9.4706380913141763E-2</v>
+      </c>
+      <c r="J20" s="119">
+        <f>1-SUM(J13:J19)</f>
+        <v>6.923644266358786E-2</v>
+      </c>
+      <c r="K20" s="119">
+        <f>1-SUM(K13:K19)</f>
+        <v>3.6403388904072242E-2</v>
+      </c>
+      <c r="L20" s="127">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A22" s="96"/>
+      <c r="B22" s="96"/>
+      <c r="E22" s="105"/>
+      <c r="K22" s="104"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C23" s="137"/>
+      <c r="D23" s="137"/>
+      <c r="E23" s="138"/>
+      <c r="F23" s="138"/>
+      <c r="G23" s="138"/>
+      <c r="J23" s="137"/>
+      <c r="K23" s="137"/>
+      <c r="L23" s="137"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A25" s="139"/>
+      <c r="B25" s="140"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="I25" s="62"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A26" s="139"/>
+      <c r="B26" s="140"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="62"/>
+      <c r="I26" s="62"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A27" s="139"/>
+      <c r="B27" s="140"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="141"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="62"/>
+      <c r="I27" s="62"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A28" s="139"/>
+      <c r="B28" s="140"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="141"/>
+      <c r="E28" s="141"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="141"/>
+      <c r="I28" s="141"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A29" s="139"/>
+      <c r="B29" s="140"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="62"/>
+      <c r="I29" s="62"/>
     </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="A25:A29"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A13:A20"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="J13:J15"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="L13:L15"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Industry data.xlsx
+++ b/Industry data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\siddhantsawant\Downloads\Strategy Tool\competitor-benchmark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC59049-1129-4BEE-884A-89DFD225B374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EA6DCCB-5BB6-4934-928A-72F4190A2297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{9699F740-2B94-447D-9E4B-153762A7606C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9699F740-2B94-447D-9E4B-153762A7606C}"/>
   </bookViews>
   <sheets>
     <sheet name="Broking data" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="332">
   <si>
     <t>Source</t>
   </si>
@@ -781,9 +781,6 @@
   </si>
   <si>
     <t>Src</t>
-  </si>
-  <si>
-    <t>MF customers</t>
   </si>
   <si>
     <t>SIF customers</t>
@@ -1113,7 +1110,7 @@
     <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0.00"/>
     <numFmt numFmtId="173" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1280,12 +1277,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1816,6 +1807,88 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="161" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="161" applyFont="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1900,46 +1973,17 @@
     <xf numFmtId="4" fontId="20" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="172" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1950,68 +1994,15 @@
     <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="161" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="161" applyFont="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="162">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -10347,7 +10338,7 @@
     <col min="31" max="31" width="16" style="8" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="16.1796875" style="8" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="14.1796875" style="8" customWidth="1"/>
-    <col min="34" max="34" width="13.08984375" style="8" customWidth="1"/>
+    <col min="34" max="34" width="14.36328125" style="8" bestFit="1" customWidth="1"/>
     <col min="35" max="37" width="8.7265625" style="8"/>
     <col min="38" max="38" width="9.453125" style="8" bestFit="1" customWidth="1"/>
     <col min="39" max="49" width="8.7265625" style="8"/>
@@ -10653,7 +10644,9 @@
       <c r="AG3" s="9">
         <v>4.7</v>
       </c>
-      <c r="AH3" s="9"/>
+      <c r="AH3" s="9">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="4" spans="1:67" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
@@ -10753,7 +10746,9 @@
       <c r="AG4" s="9">
         <v>19.100000000000001</v>
       </c>
-      <c r="AH4" s="9"/>
+      <c r="AH4" s="9">
+        <v>19.3</v>
+      </c>
     </row>
     <row r="5" spans="1:67" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
@@ -10881,7 +10876,10 @@
         <f>AG3+AG4</f>
         <v>23.8</v>
       </c>
-      <c r="AH5" s="9"/>
+      <c r="AH5" s="9">
+        <f>AH3+AH4</f>
+        <v>24</v>
+      </c>
     </row>
     <row r="6" spans="1:67" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
@@ -11008,7 +11006,10 @@
         <f>AG5-AF5</f>
         <v>0.40000000000000213</v>
       </c>
-      <c r="AH6" s="11"/>
+      <c r="AH6" s="11">
+        <f>AH5-AG5</f>
+        <v>0.19999999999999929</v>
+      </c>
     </row>
     <row r="7" spans="1:67" ht="45" x14ac:dyDescent="0.4">
       <c r="A7" s="9" t="s">
@@ -11108,7 +11109,9 @@
       <c r="AG7" s="9">
         <v>4.59</v>
       </c>
-      <c r="AH7" s="9"/>
+      <c r="AH7" s="9">
+        <v>4.6100000000000003</v>
+      </c>
     </row>
     <row r="8" spans="1:67" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
@@ -11201,10 +11204,14 @@
         <v>13.2</v>
       </c>
       <c r="AF8" s="9">
-        <v>13.1</v>
-      </c>
-      <c r="AG8" s="9"/>
-      <c r="AH8" s="9"/>
+        <v>13.4</v>
+      </c>
+      <c r="AG8" s="9">
+        <v>13.5</v>
+      </c>
+      <c r="AH8" s="9">
+        <v>13.5</v>
+      </c>
       <c r="AR8" s="16"/>
       <c r="AS8" s="16"/>
       <c r="AT8" s="16"/>
@@ -11268,7 +11275,7 @@
     </row>
     <row r="10" spans="1:67" ht="23" x14ac:dyDescent="0.4">
       <c r="A10" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -11372,7 +11379,9 @@
       <c r="AG11" s="34">
         <v>-7531.84</v>
       </c>
-      <c r="AH11" s="34"/>
+      <c r="AH11" s="34">
+        <v>-44012</v>
+      </c>
     </row>
     <row r="12" spans="1:67" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
@@ -11442,7 +11451,9 @@
       <c r="AG12" s="34">
         <v>58268.15</v>
       </c>
-      <c r="AH12" s="34"/>
+      <c r="AH12" s="34">
+        <v>76030</v>
+      </c>
     </row>
     <row r="13" spans="1:67" x14ac:dyDescent="0.4">
       <c r="A13" s="9" t="s">
@@ -11512,7 +11523,9 @@
       <c r="AG13" s="33">
         <v>-12900.29</v>
       </c>
-      <c r="AH13" s="33"/>
+      <c r="AH13" s="33">
+        <v>-20769</v>
+      </c>
     </row>
     <row r="14" spans="1:67" x14ac:dyDescent="0.4">
       <c r="A14" s="9" t="s">
@@ -11582,7 +11595,9 @@
       <c r="AG14" s="33">
         <v>-26904</v>
       </c>
-      <c r="AH14" s="33"/>
+      <c r="AH14" s="33">
+        <v>-90566</v>
+      </c>
       <c r="AL14" s="20"/>
     </row>
     <row r="15" spans="1:67" x14ac:dyDescent="0.4">
@@ -12457,8 +12472,12 @@
       <c r="AF28" s="24">
         <v>2996580.34</v>
       </c>
-      <c r="AG28" s="24"/>
-      <c r="AH28" s="24"/>
+      <c r="AG28" s="24">
+        <v>2735711</v>
+      </c>
+      <c r="AH28" s="24">
+        <v>2644322</v>
+      </c>
       <c r="AL28" s="20"/>
       <c r="AX28" s="22"/>
       <c r="AY28" s="23"/>
@@ -12563,7 +12582,9 @@
       <c r="AG29" s="24">
         <v>1281099</v>
       </c>
-      <c r="AH29" s="24"/>
+      <c r="AH29" s="24">
+        <v>1562802</v>
+      </c>
       <c r="AL29" s="20"/>
       <c r="AX29" s="22"/>
       <c r="AY29" s="23"/>
@@ -12586,7 +12607,7 @@
         <v>3630895.3270949386</v>
       </c>
       <c r="F30" s="30">
-        <f t="shared" ref="F30:AG30" si="3">F28+F29</f>
+        <f t="shared" ref="F30:AH30" si="3">F28+F29</f>
         <v>4267794.8544206629</v>
       </c>
       <c r="G30" s="30">
@@ -12695,9 +12716,12 @@
       </c>
       <c r="AG30" s="30">
         <f t="shared" si="3"/>
-        <v>1281099</v>
-      </c>
-      <c r="AH30" s="30"/>
+        <v>4016810</v>
+      </c>
+      <c r="AH30" s="30">
+        <f t="shared" si="3"/>
+        <v>4207124</v>
+      </c>
       <c r="AL30" s="20"/>
       <c r="AX30" s="22"/>
       <c r="AY30" s="23"/>
@@ -12802,7 +12826,9 @@
       <c r="AG31" s="24">
         <v>725917341.53836775</v>
       </c>
-      <c r="AH31" s="24"/>
+      <c r="AH31" s="24">
+        <v>816094572.3961941</v>
+      </c>
       <c r="AL31" s="20"/>
       <c r="AX31" s="22"/>
       <c r="AY31" s="23"/>
@@ -12917,7 +12943,7 @@
         <v>983726550</v>
       </c>
       <c r="AC32" s="30">
-        <f t="shared" ref="AC32:AG32" si="5">AC31+AC28</f>
+        <f t="shared" ref="AC32:AH32" si="5">AC31+AC28</f>
         <v>974474237</v>
       </c>
       <c r="AD32" s="30">
@@ -12934,9 +12960,12 @@
       </c>
       <c r="AG32" s="30">
         <f t="shared" si="5"/>
-        <v>725917341.53836775</v>
-      </c>
-      <c r="AH32" s="30"/>
+        <v>728653052.53836775</v>
+      </c>
+      <c r="AH32" s="30">
+        <f t="shared" si="5"/>
+        <v>818738894.3961941</v>
+      </c>
       <c r="AL32" s="20"/>
       <c r="AX32" s="22"/>
       <c r="AY32" s="23"/>
@@ -13080,7 +13109,9 @@
       <c r="AG34" s="24">
         <v>6582</v>
       </c>
-      <c r="AH34" s="24"/>
+      <c r="AH34" s="24">
+        <v>7579</v>
+      </c>
       <c r="AL34" s="20"/>
       <c r="AX34" s="22"/>
       <c r="AY34" s="23"/>
@@ -13315,7 +13346,10 @@
         <f>SUM(AG34:AG35)</f>
         <v>152506</v>
       </c>
-      <c r="AH36" s="29"/>
+      <c r="AH36" s="30">
+        <f>SUM(AH34:AH35)</f>
+        <v>7579</v>
+      </c>
       <c r="AX36" s="22"/>
       <c r="AY36" s="23"/>
       <c r="BB36" s="22"/>
@@ -13621,7 +13655,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2F2E1BA-A938-4026-BEF1-69117B3FC0AD}">
-  <dimension ref="A1:AG20"/>
+  <dimension ref="A1:AG19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -13635,12 +13669,12 @@
     <col min="29" max="29" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="8.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="15" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -13741,10 +13775,10 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A2" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="B2" s="70" t="s">
-        <v>262</v>
+        <v>238</v>
+      </c>
+      <c r="B2" s="106" t="s">
+        <v>261</v>
       </c>
       <c r="C2" s="43">
         <v>53.4</v>
@@ -13842,9 +13876,9 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="B3" s="71"/>
+        <v>239</v>
+      </c>
+      <c r="B3" s="107"/>
       <c r="C3" s="43">
         <v>23.53</v>
       </c>
@@ -13941,9 +13975,9 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A4" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="B4" s="71"/>
+        <v>232</v>
+      </c>
+      <c r="B4" s="107"/>
       <c r="C4" s="35">
         <v>1541</v>
       </c>
@@ -14040,9 +14074,9 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A5" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="B5" s="72"/>
+        <v>240</v>
+      </c>
+      <c r="B5" s="108"/>
       <c r="C5" s="43">
         <v>17.78</v>
       </c>
@@ -14174,42 +14208,42 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A7" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="B7" s="70" t="s">
-        <v>263</v>
+        <v>233</v>
+      </c>
+      <c r="B7" s="106" t="s">
+        <v>262</v>
       </c>
       <c r="C7" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="95">
+      <c r="D7" s="131">
         <v>1005.29</v>
       </c>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="95"/>
-      <c r="I7" s="95"/>
-      <c r="J7" s="95"/>
-      <c r="K7" s="95"/>
-      <c r="L7" s="95"/>
-      <c r="M7" s="95"/>
-      <c r="N7" s="95"/>
-      <c r="O7" s="95"/>
-      <c r="P7" s="75">
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="131"/>
+      <c r="J7" s="131"/>
+      <c r="K7" s="131"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="131"/>
+      <c r="N7" s="131"/>
+      <c r="O7" s="131"/>
+      <c r="P7" s="111">
         <v>1044.8399999999999</v>
       </c>
-      <c r="Q7" s="75"/>
-      <c r="R7" s="75"/>
-      <c r="S7" s="75"/>
-      <c r="T7" s="75"/>
-      <c r="U7" s="75"/>
-      <c r="V7" s="75"/>
-      <c r="W7" s="75"/>
-      <c r="X7" s="75"/>
-      <c r="Y7" s="75"/>
-      <c r="Z7" s="75"/>
-      <c r="AA7" s="76"/>
+      <c r="Q7" s="111"/>
+      <c r="R7" s="111"/>
+      <c r="S7" s="111"/>
+      <c r="T7" s="111"/>
+      <c r="U7" s="111"/>
+      <c r="V7" s="111"/>
+      <c r="W7" s="111"/>
+      <c r="X7" s="111"/>
+      <c r="Y7" s="111"/>
+      <c r="Z7" s="111"/>
+      <c r="AA7" s="112"/>
       <c r="AB7" s="53">
         <v>1044.26</v>
       </c>
@@ -14225,42 +14259,44 @@
       <c r="AF7" s="53">
         <v>1075</v>
       </c>
-      <c r="AG7" s="53"/>
+      <c r="AG7" s="53">
+        <v>1088.9000000000001</v>
+      </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A8" s="35" t="s">
-        <v>264</v>
-      </c>
-      <c r="B8" s="73"/>
+        <v>263</v>
+      </c>
+      <c r="B8" s="109"/>
       <c r="C8" s="45"/>
-      <c r="D8" s="74">
+      <c r="D8" s="110">
         <v>679.85</v>
       </c>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
-      <c r="J8" s="75"/>
-      <c r="K8" s="75"/>
-      <c r="L8" s="75"/>
-      <c r="M8" s="75"/>
-      <c r="N8" s="75"/>
-      <c r="O8" s="76"/>
-      <c r="P8" s="74">
+      <c r="E8" s="111"/>
+      <c r="F8" s="111"/>
+      <c r="G8" s="111"/>
+      <c r="H8" s="111"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="111"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="111"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="110">
         <v>719.22</v>
       </c>
-      <c r="Q8" s="75"/>
-      <c r="R8" s="75"/>
-      <c r="S8" s="75"/>
-      <c r="T8" s="75"/>
-      <c r="U8" s="75"/>
-      <c r="V8" s="75"/>
-      <c r="W8" s="75"/>
-      <c r="X8" s="75"/>
-      <c r="Y8" s="75"/>
-      <c r="Z8" s="75"/>
-      <c r="AA8" s="76"/>
+      <c r="Q8" s="111"/>
+      <c r="R8" s="111"/>
+      <c r="S8" s="111"/>
+      <c r="T8" s="111"/>
+      <c r="U8" s="111"/>
+      <c r="V8" s="111"/>
+      <c r="W8" s="111"/>
+      <c r="X8" s="111"/>
+      <c r="Y8" s="111"/>
+      <c r="Z8" s="111"/>
+      <c r="AA8" s="112"/>
       <c r="AB8" s="53">
         <v>50.71</v>
       </c>
@@ -14276,13 +14312,15 @@
       <c r="AF8" s="53">
         <v>66.400000000000006</v>
       </c>
-      <c r="AG8" s="53"/>
+      <c r="AG8" s="53">
+        <v>63.26</v>
+      </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A9" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="B9" s="71"/>
+        <v>300</v>
+      </c>
+      <c r="B9" s="107"/>
       <c r="C9" s="45">
         <v>19271</v>
       </c>
@@ -14373,44 +14411,46 @@
       <c r="AF9" s="45">
         <v>32297</v>
       </c>
-      <c r="AG9" s="45"/>
+      <c r="AG9" s="45">
+        <v>32490</v>
+      </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A10" s="35" t="s">
-        <v>302</v>
-      </c>
-      <c r="B10" s="72"/>
+        <v>301</v>
+      </c>
+      <c r="B10" s="108"/>
       <c r="C10" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="D10" s="92">
+      <c r="D10" s="128">
         <v>1335188</v>
       </c>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="93"/>
-      <c r="I10" s="93"/>
-      <c r="J10" s="93"/>
-      <c r="K10" s="93"/>
-      <c r="L10" s="93"/>
-      <c r="M10" s="93"/>
-      <c r="N10" s="93"/>
-      <c r="O10" s="94"/>
-      <c r="P10" s="92">
+      <c r="E10" s="129"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="129"/>
+      <c r="J10" s="129"/>
+      <c r="K10" s="129"/>
+      <c r="L10" s="129"/>
+      <c r="M10" s="129"/>
+      <c r="N10" s="129"/>
+      <c r="O10" s="130"/>
+      <c r="P10" s="128">
         <v>1510943</v>
       </c>
-      <c r="Q10" s="93"/>
-      <c r="R10" s="93"/>
-      <c r="S10" s="93"/>
-      <c r="T10" s="93"/>
-      <c r="U10" s="93"/>
-      <c r="V10" s="93"/>
-      <c r="W10" s="93"/>
-      <c r="X10" s="93"/>
-      <c r="Y10" s="93"/>
-      <c r="Z10" s="93"/>
-      <c r="AA10" s="94"/>
+      <c r="Q10" s="129"/>
+      <c r="R10" s="129"/>
+      <c r="S10" s="129"/>
+      <c r="T10" s="129"/>
+      <c r="U10" s="129"/>
+      <c r="V10" s="129"/>
+      <c r="W10" s="129"/>
+      <c r="X10" s="129"/>
+      <c r="Y10" s="129"/>
+      <c r="Z10" s="129"/>
+      <c r="AA10" s="130"/>
       <c r="AB10" s="45">
         <v>1685126</v>
       </c>
@@ -14426,7 +14466,9 @@
       <c r="AF10" s="45">
         <v>1861652</v>
       </c>
-      <c r="AG10" s="45"/>
+      <c r="AG10" s="45">
+        <v>1786095</v>
+      </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A11" s="35"/>
@@ -14464,9 +14506,7 @@
       <c r="AG11" s="35"/>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A12" s="35" t="s">
-        <v>229</v>
-      </c>
+      <c r="A12" s="35"/>
       <c r="B12" s="35"/>
       <c r="C12" s="35"/>
       <c r="D12" s="35"/>
@@ -14501,433 +14541,402 @@
       <c r="AG12" s="35"/>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A13" s="35"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="35"/>
-      <c r="V13" s="35"/>
-      <c r="W13" s="35"/>
-      <c r="X13" s="35"/>
-      <c r="Y13" s="35"/>
-      <c r="Z13" s="35"/>
-      <c r="AA13" s="35"/>
-      <c r="AB13" s="35"/>
-      <c r="AC13" s="35"/>
-      <c r="AD13" s="35"/>
-      <c r="AE13" s="35"/>
-      <c r="AF13" s="35"/>
-      <c r="AG13" s="35"/>
+      <c r="A13" s="35" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" s="106" t="s">
+        <v>264</v>
+      </c>
+      <c r="C13" s="113" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="114"/>
+      <c r="E13" s="114"/>
+      <c r="F13" s="114"/>
+      <c r="G13" s="114"/>
+      <c r="H13" s="114"/>
+      <c r="I13" s="114"/>
+      <c r="J13" s="114"/>
+      <c r="K13" s="114"/>
+      <c r="L13" s="114"/>
+      <c r="M13" s="114"/>
+      <c r="N13" s="114"/>
+      <c r="O13" s="114"/>
+      <c r="P13" s="114"/>
+      <c r="Q13" s="114"/>
+      <c r="R13" s="114"/>
+      <c r="S13" s="114"/>
+      <c r="T13" s="114"/>
+      <c r="U13" s="115"/>
+      <c r="V13" s="45">
+        <v>2010.4352133</v>
+      </c>
+      <c r="W13" s="45">
+        <v>2931.71</v>
+      </c>
+      <c r="X13" s="45">
+        <v>4892.32</v>
+      </c>
+      <c r="Y13" s="45">
+        <v>6564.24</v>
+      </c>
+      <c r="Z13" s="45">
+        <v>9710.8700000000008</v>
+      </c>
+      <c r="AA13" s="45">
+        <v>10620.45</v>
+      </c>
+      <c r="AB13" s="45">
+        <v>12329.05</v>
+      </c>
+      <c r="AC13" s="45">
+        <v>13813.72</v>
+      </c>
+      <c r="AD13" s="45">
+        <v>17857.77</v>
+      </c>
+      <c r="AE13" s="45">
+        <v>23177.31</v>
+      </c>
+      <c r="AF13" s="45">
+        <v>31175.43</v>
+      </c>
+      <c r="AG13" s="45">
+        <v>38286</v>
+      </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A14" s="35" t="s">
-        <v>300</v>
-      </c>
-      <c r="B14" s="70" t="s">
-        <v>265</v>
-      </c>
-      <c r="C14" s="77" t="s">
-        <v>155</v>
-      </c>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="78"/>
-      <c r="M14" s="78"/>
-      <c r="N14" s="78"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="78"/>
-      <c r="Q14" s="78"/>
-      <c r="R14" s="78"/>
-      <c r="S14" s="78"/>
-      <c r="T14" s="78"/>
-      <c r="U14" s="79"/>
+        <v>234</v>
+      </c>
+      <c r="B14" s="107"/>
+      <c r="C14" s="116"/>
+      <c r="D14" s="117"/>
+      <c r="E14" s="117"/>
+      <c r="F14" s="117"/>
+      <c r="G14" s="117"/>
+      <c r="H14" s="117"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="117"/>
+      <c r="L14" s="117"/>
+      <c r="M14" s="117"/>
+      <c r="N14" s="117"/>
+      <c r="O14" s="117"/>
+      <c r="P14" s="117"/>
+      <c r="Q14" s="117"/>
+      <c r="R14" s="117"/>
+      <c r="S14" s="117"/>
+      <c r="T14" s="117"/>
+      <c r="U14" s="118"/>
       <c r="V14" s="45">
-        <v>2010.4352133</v>
+        <v>10212</v>
       </c>
       <c r="W14" s="45">
-        <v>2931.71</v>
+        <v>14712</v>
       </c>
       <c r="X14" s="45">
-        <v>4892.32</v>
+        <v>20779</v>
       </c>
       <c r="Y14" s="45">
-        <v>6564.24</v>
+        <v>24372</v>
       </c>
       <c r="Z14" s="45">
-        <v>9710.8700000000008</v>
+        <v>39851</v>
       </c>
       <c r="AA14" s="45">
-        <v>10620.45</v>
+        <v>44573</v>
       </c>
       <c r="AB14" s="45">
-        <v>12329.05</v>
+        <v>50096</v>
       </c>
       <c r="AC14" s="45">
-        <v>13813.72</v>
+        <v>56749</v>
       </c>
       <c r="AD14" s="45">
-        <v>17857.77</v>
+        <v>75032</v>
       </c>
       <c r="AE14" s="45">
-        <v>23177.31</v>
+        <v>94447</v>
       </c>
       <c r="AF14" s="45">
-        <v>31175.43</v>
+        <v>125539</v>
       </c>
       <c r="AG14" s="45">
-        <v>38286</v>
+        <v>156483</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A15" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="81"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="81"/>
-      <c r="L15" s="81"/>
-      <c r="M15" s="81"/>
-      <c r="N15" s="81"/>
-      <c r="O15" s="81"/>
-      <c r="P15" s="81"/>
-      <c r="Q15" s="81"/>
-      <c r="R15" s="81"/>
-      <c r="S15" s="81"/>
-      <c r="T15" s="81"/>
-      <c r="U15" s="82"/>
+      <c r="B15" s="107"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="117"/>
+      <c r="L15" s="117"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="117"/>
+      <c r="O15" s="117"/>
+      <c r="P15" s="117"/>
+      <c r="Q15" s="117"/>
+      <c r="R15" s="117"/>
+      <c r="S15" s="117"/>
+      <c r="T15" s="117"/>
+      <c r="U15" s="118"/>
       <c r="V15" s="45">
-        <v>10212</v>
+        <v>4</v>
       </c>
       <c r="W15" s="45">
-        <v>14712</v>
+        <v>5</v>
       </c>
       <c r="X15" s="45">
-        <v>20779</v>
+        <v>7</v>
       </c>
       <c r="Y15" s="45">
-        <v>24372</v>
+        <v>8</v>
       </c>
       <c r="Z15" s="45">
-        <v>39851</v>
+        <v>11</v>
       </c>
       <c r="AA15" s="45">
-        <v>44573</v>
+        <v>14</v>
       </c>
       <c r="AB15" s="45">
-        <v>50096</v>
+        <v>16</v>
       </c>
       <c r="AC15" s="45">
-        <v>56749</v>
-      </c>
-      <c r="AD15" s="45">
-        <v>75032</v>
+        <v>21</v>
+      </c>
+      <c r="AD15" s="47">
+        <v>27</v>
       </c>
       <c r="AE15" s="45">
-        <v>94447</v>
+        <v>30</v>
       </c>
       <c r="AF15" s="45">
-        <v>125539</v>
+        <v>33</v>
       </c>
       <c r="AG15" s="45">
-        <v>156483</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A16" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="B16" s="108"/>
+      <c r="C16" s="119"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120"/>
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="120"/>
+      <c r="P16" s="120"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="120"/>
+      <c r="S16" s="120"/>
+      <c r="T16" s="120"/>
+      <c r="U16" s="121"/>
+      <c r="V16" s="45"/>
+      <c r="W16" s="45"/>
+      <c r="X16" s="45"/>
+      <c r="Y16" s="45"/>
+      <c r="Z16" s="45"/>
+      <c r="AA16" s="45"/>
+      <c r="AB16" s="45"/>
+      <c r="AC16" s="45"/>
+      <c r="AD16" s="45"/>
+      <c r="AE16" s="45"/>
+      <c r="AF16" s="45"/>
+      <c r="AG16" s="45"/>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A17" s="35"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="35"/>
+      <c r="U17" s="35"/>
+      <c r="V17" s="35"/>
+      <c r="W17" s="35"/>
+      <c r="X17" s="35"/>
+      <c r="Y17" s="35"/>
+      <c r="Z17" s="35"/>
+      <c r="AA17" s="35"/>
+      <c r="AB17" s="35"/>
+      <c r="AC17" s="35"/>
+      <c r="AD17" s="35"/>
+      <c r="AE17" s="35"/>
+      <c r="AF17" s="35"/>
+      <c r="AG17" s="35"/>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A18" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="80"/>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="81"/>
-      <c r="U16" s="82"/>
-      <c r="V16" s="45">
-        <v>4</v>
-      </c>
-      <c r="W16" s="45">
-        <v>5</v>
-      </c>
-      <c r="X16" s="45">
-        <v>7</v>
-      </c>
-      <c r="Y16" s="45">
-        <v>8</v>
-      </c>
-      <c r="Z16" s="45">
-        <v>11</v>
-      </c>
-      <c r="AA16" s="45">
-        <v>14</v>
-      </c>
-      <c r="AB16" s="45">
-        <v>16</v>
-      </c>
-      <c r="AC16" s="45">
-        <v>21</v>
-      </c>
-      <c r="AD16" s="47">
-        <v>27</v>
-      </c>
-      <c r="AE16" s="45">
-        <v>30</v>
-      </c>
-      <c r="AF16" s="45">
-        <v>33</v>
-      </c>
-      <c r="AG16" s="45">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A17" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="B17" s="72"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="84"/>
-      <c r="E17" s="84"/>
-      <c r="F17" s="84"/>
-      <c r="G17" s="84"/>
-      <c r="H17" s="84"/>
-      <c r="I17" s="84"/>
-      <c r="J17" s="84"/>
-      <c r="K17" s="84"/>
-      <c r="L17" s="84"/>
-      <c r="M17" s="84"/>
-      <c r="N17" s="84"/>
-      <c r="O17" s="84"/>
-      <c r="P17" s="84"/>
-      <c r="Q17" s="84"/>
-      <c r="R17" s="84"/>
-      <c r="S17" s="84"/>
-      <c r="T17" s="84"/>
-      <c r="U17" s="85"/>
-      <c r="V17" s="45"/>
-      <c r="W17" s="45"/>
-      <c r="X17" s="45"/>
-      <c r="Y17" s="45"/>
-      <c r="Z17" s="45"/>
-      <c r="AA17" s="45"/>
-      <c r="AB17" s="45"/>
-      <c r="AC17" s="45"/>
-      <c r="AD17" s="45"/>
-      <c r="AE17" s="45"/>
-      <c r="AF17" s="45"/>
-      <c r="AG17" s="45"/>
-    </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A18" s="35"/>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="35"/>
-      <c r="U18" s="35"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="35"/>
-      <c r="X18" s="35"/>
-      <c r="Y18" s="35"/>
-      <c r="Z18" s="35"/>
-      <c r="AA18" s="35"/>
-      <c r="AB18" s="35"/>
-      <c r="AC18" s="35"/>
-      <c r="AD18" s="35"/>
-      <c r="AE18" s="35"/>
-      <c r="AF18" s="35"/>
-      <c r="AG18" s="35"/>
+      <c r="B18" s="104"/>
+      <c r="C18" s="122" t="s">
+        <v>155</v>
+      </c>
+      <c r="D18" s="123"/>
+      <c r="E18" s="123"/>
+      <c r="F18" s="123"/>
+      <c r="G18" s="123"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="123"/>
+      <c r="J18" s="123"/>
+      <c r="K18" s="123"/>
+      <c r="L18" s="123"/>
+      <c r="M18" s="123"/>
+      <c r="N18" s="123"/>
+      <c r="O18" s="123"/>
+      <c r="P18" s="123"/>
+      <c r="Q18" s="123"/>
+      <c r="R18" s="123"/>
+      <c r="S18" s="123"/>
+      <c r="T18" s="124"/>
+      <c r="U18" s="35">
+        <v>14.47</v>
+      </c>
+      <c r="V18" s="35">
+        <v>15.19</v>
+      </c>
+      <c r="W18" s="35">
+        <v>15.32</v>
+      </c>
+      <c r="X18" s="35">
+        <v>15.35</v>
+      </c>
+      <c r="Y18" s="35">
+        <v>15.32</v>
+      </c>
+      <c r="Z18" s="35">
+        <v>15.5</v>
+      </c>
+      <c r="AA18" s="35">
+        <v>13.89</v>
+      </c>
+      <c r="AB18" s="35">
+        <v>15.35</v>
+      </c>
+      <c r="AC18" s="35">
+        <v>15.57</v>
+      </c>
+      <c r="AD18" s="35">
+        <v>15.88</v>
+      </c>
+      <c r="AE18" s="35">
+        <v>16.29</v>
+      </c>
+      <c r="AF18" s="35">
+        <v>16.55</v>
+      </c>
+      <c r="AG18" s="35">
+        <v>15.7</v>
+      </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A19" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="B19" s="68"/>
-      <c r="C19" s="86" t="s">
-        <v>155</v>
-      </c>
-      <c r="D19" s="87"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="87"/>
-      <c r="I19" s="87"/>
-      <c r="J19" s="87"/>
-      <c r="K19" s="87"/>
-      <c r="L19" s="87"/>
-      <c r="M19" s="87"/>
-      <c r="N19" s="87"/>
-      <c r="O19" s="87"/>
-      <c r="P19" s="87"/>
-      <c r="Q19" s="87"/>
-      <c r="R19" s="87"/>
-      <c r="S19" s="87"/>
-      <c r="T19" s="88"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="126"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="126"/>
+      <c r="H19" s="126"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="126"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="126"/>
+      <c r="O19" s="126"/>
+      <c r="P19" s="126"/>
+      <c r="Q19" s="126"/>
+      <c r="R19" s="126"/>
+      <c r="S19" s="126"/>
+      <c r="T19" s="127"/>
       <c r="U19" s="35">
-        <v>14.47</v>
+        <v>61.14</v>
       </c>
       <c r="V19" s="35">
-        <v>15.19</v>
+        <v>64.69</v>
       </c>
       <c r="W19" s="35">
-        <v>15.32</v>
+        <v>65.48</v>
       </c>
       <c r="X19" s="35">
-        <v>15.35</v>
+        <v>64.88</v>
       </c>
       <c r="Y19" s="35">
-        <v>15.32</v>
+        <v>65.7</v>
       </c>
       <c r="Z19" s="35">
-        <v>15.5</v>
+        <v>66.53</v>
       </c>
       <c r="AA19" s="35">
-        <v>13.89</v>
+        <v>59.84</v>
       </c>
       <c r="AB19" s="35">
-        <v>15.35</v>
+        <v>66.569999999999993</v>
       </c>
       <c r="AC19" s="35">
-        <v>15.57</v>
+        <v>66.02</v>
       </c>
       <c r="AD19" s="35">
-        <v>15.88</v>
+        <v>66.349999999999994</v>
       </c>
       <c r="AE19" s="35">
-        <v>16.29</v>
+        <v>69.47</v>
       </c>
       <c r="AF19" s="35">
-        <v>16.55</v>
-      </c>
-      <c r="AG19" s="35"/>
-    </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A20" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="B20" s="69"/>
-      <c r="C20" s="89"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="90"/>
-      <c r="J20" s="90"/>
-      <c r="K20" s="90"/>
-      <c r="L20" s="90"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="90"/>
-      <c r="O20" s="90"/>
-      <c r="P20" s="90"/>
-      <c r="Q20" s="90"/>
-      <c r="R20" s="90"/>
-      <c r="S20" s="90"/>
-      <c r="T20" s="91"/>
-      <c r="U20" s="35">
-        <v>61.14</v>
-      </c>
-      <c r="V20" s="35">
-        <v>64.69</v>
-      </c>
-      <c r="W20" s="35">
-        <v>65.48</v>
-      </c>
-      <c r="X20" s="35">
-        <v>64.88</v>
-      </c>
-      <c r="Y20" s="35">
-        <v>65.7</v>
-      </c>
-      <c r="Z20" s="35">
-        <v>66.53</v>
-      </c>
-      <c r="AA20" s="35">
-        <v>59.84</v>
-      </c>
-      <c r="AB20" s="35">
-        <v>66.569999999999993</v>
-      </c>
-      <c r="AC20" s="35">
-        <v>66.02</v>
-      </c>
-      <c r="AD20" s="35">
-        <v>66.349999999999994</v>
-      </c>
-      <c r="AE20" s="35">
-        <v>69.47</v>
-      </c>
-      <c r="AF20" s="35">
         <v>70.53</v>
       </c>
-      <c r="AG20" s="35"/>
+      <c r="AG19" s="35">
+        <v>66.94</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="B7:B10"/>
     <mergeCell ref="P8:AA8"/>
     <mergeCell ref="D8:O8"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C14:U17"/>
-    <mergeCell ref="C19:T20"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="C13:U16"/>
+    <mergeCell ref="C18:T19"/>
     <mergeCell ref="P10:AA10"/>
     <mergeCell ref="D10:O10"/>
     <mergeCell ref="P7:AA7"/>
@@ -14936,7 +14945,7 @@
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{3F2511E2-5345-4696-A6E1-2B48A4EF8B21}"/>
     <hyperlink ref="B7" r:id="rId2" xr:uid="{326DDE7D-9B61-4C7B-A184-1F0291A14240}"/>
-    <hyperlink ref="B14" r:id="rId3" xr:uid="{CA7654E3-BA04-4EAA-B079-74555F38E039}"/>
+    <hyperlink ref="B13" r:id="rId3" xr:uid="{CA7654E3-BA04-4EAA-B079-74555F38E039}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14995,10 +15004,10 @@
         <v>46266</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.4">
@@ -15250,7 +15259,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B11" s="49">
         <v>1051951</v>
@@ -15538,7 +15547,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B20" s="49">
         <v>150011</v>
@@ -15809,7 +15818,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B29" s="52">
         <v>67432</v>
@@ -16088,7 +16097,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B39" s="49">
         <v>66717</v>
@@ -16563,7 +16572,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B56" s="49">
         <v>49090</v>
@@ -16646,7 +16655,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B59" s="49" t="s">
         <v>132</v>
@@ -17345,7 +17354,7 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A84" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B84" s="49" t="s">
         <v>155</v>
@@ -17821,7 +17830,7 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A101" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B101" s="49" t="s">
         <v>155</v>
@@ -17849,7 +17858,7 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A102" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B102" s="49" t="s">
         <v>155</v>
@@ -17933,7 +17942,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A105" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B105" s="49" t="s">
         <v>155</v>
@@ -18045,7 +18054,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A109" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B109" s="49" t="s">
         <v>155</v>
@@ -18465,7 +18474,7 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A124" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B124" s="49" t="s">
         <v>155</v>
@@ -18549,7 +18558,7 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A127" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B127" s="49" t="s">
         <v>155</v>
@@ -18772,7 +18781,7 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A135" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B135" s="49" t="s">
         <v>155</v>
@@ -19024,7 +19033,7 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A144" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B144" s="49" t="s">
         <v>132</v>
@@ -19388,7 +19397,7 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A157" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B157" s="49" t="s">
         <v>155</v>
@@ -19671,7 +19680,7 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A167" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B167" s="49" t="s">
         <v>155</v>
@@ -19927,7 +19936,7 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A176" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B176" s="49" t="s">
         <v>155</v>
@@ -20662,7 +20671,7 @@
     </row>
     <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A202" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B202" s="49" t="s">
         <v>155</v>
@@ -20688,7 +20697,7 @@
     </row>
     <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A203" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B203" s="49" t="s">
         <v>155</v>
@@ -20870,13 +20879,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="55" t="s">
+        <v>265</v>
+      </c>
+      <c r="B1" s="55" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="C1" s="55" t="s">
         <v>267</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.35">
@@ -20884,10 +20893,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="C2" t="s">
         <v>269</v>
-      </c>
-      <c r="C2" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -20895,10 +20904,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C3" t="s">
         <v>271</v>
-      </c>
-      <c r="C3" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -20906,10 +20915,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>272</v>
+      </c>
+      <c r="C4" t="s">
         <v>273</v>
-      </c>
-      <c r="C4" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -20920,7 +20929,7 @@
         <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -20928,10 +20937,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6" t="s">
         <v>276</v>
-      </c>
-      <c r="C6" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -20939,10 +20948,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C7" t="s">
         <v>278</v>
-      </c>
-      <c r="C7" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -20950,10 +20959,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" t="s">
         <v>280</v>
-      </c>
-      <c r="C8" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -20961,10 +20970,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>281</v>
+      </c>
+      <c r="C9" t="s">
         <v>282</v>
-      </c>
-      <c r="C9" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -20972,10 +20981,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C10" t="s">
         <v>284</v>
-      </c>
-      <c r="C10" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -20983,10 +20992,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>285</v>
+      </c>
+      <c r="C11" t="s">
         <v>286</v>
-      </c>
-      <c r="C11" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -20994,10 +21003,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>287</v>
+      </c>
+      <c r="C12" t="s">
         <v>288</v>
-      </c>
-      <c r="C12" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -21005,10 +21014,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>289</v>
+      </c>
+      <c r="C13" t="s">
         <v>290</v>
-      </c>
-      <c r="C13" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -21016,10 +21025,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>291</v>
+      </c>
+      <c r="C14" t="s">
         <v>292</v>
-      </c>
-      <c r="C14" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -21027,10 +21036,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>293</v>
+      </c>
+      <c r="C15" t="s">
         <v>294</v>
-      </c>
-      <c r="C15" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -21038,10 +21047,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>295</v>
+      </c>
+      <c r="C16" t="s">
         <v>296</v>
-      </c>
-      <c r="C16" t="s">
-        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -21074,146 +21083,146 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="B1" s="68"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C2" s="134" t="s">
         <v>306</v>
       </c>
-      <c r="B1" s="96"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="C2" s="97" t="s">
+      <c r="D2" s="134"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="J2" s="134" t="s">
         <v>307</v>
       </c>
-      <c r="D2" s="97"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="J2" s="97" t="s">
+      <c r="K2" s="134"/>
+      <c r="L2" s="134"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C3" s="70" t="s">
+        <v>302</v>
+      </c>
+      <c r="D3" s="70" t="s">
         <v>308</v>
       </c>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="C3" s="99" t="s">
-        <v>303</v>
-      </c>
-      <c r="D3" s="99" t="s">
+      <c r="E3" s="70" t="s">
+        <v>304</v>
+      </c>
+      <c r="F3" s="70" t="s">
         <v>309</v>
       </c>
-      <c r="E3" s="99" t="s">
-        <v>305</v>
-      </c>
-      <c r="F3" s="99" t="s">
+      <c r="G3" s="71"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="70" t="s">
         <v>310</v>
       </c>
-      <c r="G3" s="100"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="99" t="s">
+      <c r="J3" s="70" t="s">
         <v>311</v>
       </c>
-      <c r="J3" s="99" t="s">
+      <c r="K3" s="70" t="s">
         <v>312</v>
       </c>
-      <c r="K3" s="99" t="s">
+      <c r="L3" s="70" t="s">
         <v>313</v>
       </c>
-      <c r="L3" s="99" t="s">
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="73" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="102" t="s">
-        <v>315</v>
-      </c>
-      <c r="C4" s="103">
+      <c r="C4" s="74">
         <v>4644.5</v>
       </c>
-      <c r="D4" s="104">
+      <c r="D4" s="75">
         <v>5072</v>
       </c>
-      <c r="E4" s="103">
+      <c r="E4" s="74">
         <v>7464</v>
       </c>
-      <c r="F4" s="104">
+      <c r="F4" s="75">
         <v>1069.6300000000001</v>
       </c>
-      <c r="G4" s="104"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="103">
+      <c r="G4" s="75"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="74">
         <v>4890</v>
       </c>
-      <c r="J4" s="103">
+      <c r="J4" s="74">
         <v>5889.8</v>
       </c>
-      <c r="K4" s="103">
+      <c r="K4" s="74">
         <v>3110.15</v>
       </c>
-      <c r="L4" s="103">
+      <c r="L4" s="74">
         <f>546149.37/100</f>
         <v>5461.4937</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="73" t="s">
+        <v>315</v>
+      </c>
+      <c r="C5" s="74">
+        <v>2083</v>
+      </c>
+      <c r="D5" s="75">
+        <v>1022.7</v>
+      </c>
+      <c r="E5" s="74">
+        <v>4283</v>
+      </c>
+      <c r="F5" s="75">
+        <v>202.57</v>
+      </c>
+      <c r="G5" s="75"/>
+      <c r="I5" s="74">
+        <v>922.51</v>
+      </c>
+      <c r="J5" s="74">
+        <v>1713.1</v>
+      </c>
+      <c r="K5" s="74">
+        <v>929.99400000000003</v>
+      </c>
+      <c r="L5" s="74">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="73" t="s">
         <v>316</v>
       </c>
-      <c r="C5" s="103">
-        <v>2083</v>
-      </c>
-      <c r="D5" s="104">
-        <v>1022.7</v>
-      </c>
-      <c r="E5" s="103">
-        <v>4283</v>
-      </c>
-      <c r="F5" s="104">
-        <v>202.57</v>
-      </c>
-      <c r="G5" s="104"/>
-      <c r="I5" s="103">
-        <v>922.51</v>
-      </c>
-      <c r="J5" s="103">
-        <v>1713.1</v>
-      </c>
-      <c r="K5" s="103">
-        <v>929.99400000000003</v>
-      </c>
-      <c r="L5" s="103">
-        <v>1664</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="102" t="s">
-        <v>317</v>
-      </c>
-      <c r="C6" s="103">
+      <c r="C6" s="74">
         <f>48554.45/10</f>
         <v>4855.4449999999997</v>
       </c>
-      <c r="D6" s="104">
+      <c r="D6" s="75">
         <f>(55075.74+903)/10</f>
         <v>5597.8739999999998</v>
       </c>
-      <c r="E6" s="106">
+      <c r="E6" s="77">
         <v>16500</v>
       </c>
-      <c r="F6" s="104">
+      <c r="F6" s="75">
         <v>1288.93</v>
       </c>
-      <c r="G6" s="104"/>
-      <c r="I6" s="103">
+      <c r="G6" s="75"/>
+      <c r="I6" s="74">
         <f>711687/100</f>
         <v>7116.87</v>
       </c>
-      <c r="J6" s="103">
+      <c r="J6" s="74">
         <f>54220.6/10</f>
         <v>5422.0599999999995</v>
       </c>
-      <c r="K6" s="103">
+      <c r="K6" s="74">
         <v>3348.59</v>
       </c>
-      <c r="L6" s="103">
+      <c r="L6" s="74">
         <f>1000868.33/100</f>
         <v>10008.683299999999</v>
       </c>
@@ -21222,36 +21231,36 @@
       </c>
     </row>
     <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="102" t="s">
+      <c r="A7" s="73" t="s">
+        <v>317</v>
+      </c>
+      <c r="B7" s="78" t="s">
         <v>318</v>
       </c>
-      <c r="B7" s="107" t="s">
-        <v>319</v>
-      </c>
-      <c r="C7" s="103">
+      <c r="C7" s="74">
         <v>9651.4000000000015</v>
       </c>
-      <c r="D7" s="104">
+      <c r="D7" s="75">
         <v>6201.9</v>
       </c>
-      <c r="E7" s="103">
+      <c r="E7" s="74">
         <f>E6+E5</f>
         <v>20783</v>
       </c>
-      <c r="F7" s="104">
+      <c r="F7" s="75">
         <v>2085.9699999999998</v>
       </c>
-      <c r="G7" s="104"/>
-      <c r="I7" s="103">
+      <c r="G7" s="75"/>
+      <c r="I7" s="74">
         <v>7950.56</v>
       </c>
-      <c r="J7" s="103">
+      <c r="J7" s="74">
         <v>6294.5</v>
       </c>
-      <c r="K7" s="103">
+      <c r="K7" s="74">
         <v>3595.92</v>
       </c>
-      <c r="L7" s="103">
+      <c r="L7" s="74">
         <v>11614.4</v>
       </c>
       <c r="P7">
@@ -21259,40 +21268,40 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A8" s="102" t="s">
-        <v>320</v>
-      </c>
-      <c r="B8" s="107"/>
-      <c r="C8" s="103">
+      <c r="A8" s="73" t="s">
+        <v>319</v>
+      </c>
+      <c r="B8" s="78"/>
+      <c r="C8" s="74">
         <f>AVERAGE(C6:C7)</f>
         <v>7253.4225000000006</v>
       </c>
-      <c r="D8" s="103">
+      <c r="D8" s="74">
         <f t="shared" ref="D8:L8" si="0">AVERAGE(D6:D7)</f>
         <v>5899.8869999999997</v>
       </c>
-      <c r="E8" s="103">
+      <c r="E8" s="74">
         <f t="shared" si="0"/>
         <v>18641.5</v>
       </c>
-      <c r="F8" s="103">
+      <c r="F8" s="74">
         <v>1687.45</v>
       </c>
-      <c r="G8" s="104"/>
-      <c r="H8" s="104"/>
-      <c r="I8" s="103">
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="74">
         <f t="shared" si="0"/>
         <v>7533.7150000000001</v>
       </c>
-      <c r="J8" s="103">
+      <c r="J8" s="74">
         <f t="shared" si="0"/>
         <v>5858.28</v>
       </c>
-      <c r="K8" s="103">
+      <c r="K8" s="74">
         <f t="shared" si="0"/>
         <v>3472.2550000000001</v>
       </c>
-      <c r="L8" s="103">
+      <c r="L8" s="74">
         <f t="shared" si="0"/>
         <v>10811.541649999999</v>
       </c>
@@ -21301,39 +21310,39 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A9" s="102" t="s">
-        <v>304</v>
-      </c>
-      <c r="C9" s="108">
+      <c r="A9" s="73" t="s">
+        <v>303</v>
+      </c>
+      <c r="C9" s="79">
         <f>C5/AVERAGE(C6,C7)</f>
         <v>0.28717477852696432</v>
       </c>
-      <c r="D9" s="109">
+      <c r="D9" s="80">
         <f>D5/AVERAGE(D6:D7)</f>
         <v>0.17334230299665063</v>
       </c>
-      <c r="E9" s="108">
+      <c r="E9" s="79">
         <f>E5/AVERAGE(E6:E7)</f>
         <v>0.22975618914786899</v>
       </c>
-      <c r="F9" s="108">
+      <c r="F9" s="79">
         <f>F5/AVERAGE(F6:F7)</f>
         <v>0.12004503837150732</v>
       </c>
-      <c r="G9" s="110"/>
-      <c r="I9" s="108">
+      <c r="G9" s="81"/>
+      <c r="I9" s="79">
         <f>I5/AVERAGE(I6:I7)</f>
         <v>0.12245087582952102</v>
       </c>
-      <c r="J9" s="108">
+      <c r="J9" s="79">
         <f>J5/AVERAGE(J6:J7)</f>
         <v>0.29242371481049045</v>
       </c>
-      <c r="K9" s="108">
+      <c r="K9" s="79">
         <f>K5/AVERAGE(K6:K7)</f>
         <v>0.2678357436305801</v>
       </c>
-      <c r="L9" s="108">
+      <c r="L9" s="79">
         <f>L5/AVERAGE(L6:L7)</f>
         <v>0.15390959530734455</v>
       </c>
@@ -21341,234 +21350,234 @@
         <f>P6-P7-P8</f>
         <v>831</v>
       </c>
-      <c r="Q9" s="105">
+      <c r="Q9" s="76">
         <f>P9/P6</f>
         <v>0.79218303145853197</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A10" s="102" t="s">
-        <v>321</v>
-      </c>
-      <c r="C10" s="103">
+      <c r="A10" s="73" t="s">
+        <v>320</v>
+      </c>
+      <c r="C10" s="74">
         <v>2814.2</v>
       </c>
-      <c r="D10" s="104">
+      <c r="D10" s="75">
         <v>5128</v>
       </c>
-      <c r="E10" s="106">
+      <c r="E10" s="77">
         <v>7000</v>
       </c>
-      <c r="F10" s="111">
+      <c r="F10" s="82">
         <v>7985</v>
       </c>
-      <c r="I10" s="103">
+      <c r="I10" s="74">
         <v>5767.36</v>
       </c>
-      <c r="J10" s="103">
+      <c r="J10" s="74">
         <v>14561.34</v>
       </c>
-      <c r="K10" s="103">
+      <c r="K10" s="74">
         <v>7132.66</v>
       </c>
-      <c r="L10" s="103">
+      <c r="L10" s="74">
         <v>13363.15</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="O11" s="104"/>
+      <c r="O11" s="75"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B12" s="35"/>
-      <c r="C12" s="112" t="s">
-        <v>303</v>
-      </c>
-      <c r="D12" s="112" t="s">
+      <c r="C12" s="83" t="s">
+        <v>302</v>
+      </c>
+      <c r="D12" s="83" t="s">
+        <v>308</v>
+      </c>
+      <c r="E12" s="83" t="s">
+        <v>304</v>
+      </c>
+      <c r="F12" s="70" t="s">
         <v>309</v>
       </c>
-      <c r="E12" s="112" t="s">
-        <v>305</v>
-      </c>
-      <c r="F12" s="99" t="s">
+      <c r="G12" s="71"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="70" t="s">
         <v>310</v>
       </c>
-      <c r="G12" s="100"/>
-      <c r="H12" s="101"/>
-      <c r="I12" s="99" t="s">
+      <c r="J12" s="70" t="s">
         <v>311</v>
       </c>
-      <c r="J12" s="99" t="s">
+      <c r="K12" s="70" t="s">
         <v>312</v>
       </c>
-      <c r="K12" s="99" t="s">
+      <c r="L12" s="70" t="s">
         <v>313</v>
       </c>
-      <c r="L12" s="99" t="s">
-        <v>314</v>
-      </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A13" s="113" t="s">
+      <c r="A13" s="135" t="s">
+        <v>321</v>
+      </c>
+      <c r="B13" s="85" t="s">
         <v>322</v>
       </c>
-      <c r="B13" s="114" t="s">
-        <v>323</v>
-      </c>
-      <c r="C13" s="115">
+      <c r="C13" s="86">
         <v>0.55120000000000002</v>
       </c>
-      <c r="D13" s="116">
+      <c r="D13" s="87">
         <v>0.45500000000000002</v>
       </c>
-      <c r="E13" s="117">
+      <c r="E13" s="136">
         <v>0.36699999999999999</v>
       </c>
       <c r="F13" s="50">
         <v>3.0499999999999999E-2</v>
       </c>
       <c r="G13" s="50"/>
-      <c r="H13" s="118" t="s">
-        <v>324</v>
-      </c>
-      <c r="I13" s="119">
+      <c r="H13" s="137" t="s">
+        <v>323</v>
+      </c>
+      <c r="I13" s="89">
         <f t="shared" ref="I13:I19" si="1">P13/$I$4</f>
         <v>0.15912603524401842</v>
       </c>
-      <c r="J13" s="120">
+      <c r="J13" s="138">
         <v>0.28199999999999997</v>
       </c>
-      <c r="K13" s="120">
+      <c r="K13" s="138">
         <f>1012/K4</f>
         <v>0.32538623539057598</v>
       </c>
-      <c r="L13" s="120">
+      <c r="L13" s="138">
         <v>0.44</v>
       </c>
-      <c r="M13" s="121"/>
+      <c r="M13" s="90"/>
       <c r="P13" s="39">
         <f>[2]Consol!$S$52</f>
         <v>778.12631234324999</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A14" s="113"/>
-      <c r="B14" s="114" t="s">
-        <v>325</v>
-      </c>
-      <c r="C14" s="115">
+      <c r="A14" s="135"/>
+      <c r="B14" s="85" t="s">
+        <v>324</v>
+      </c>
+      <c r="C14" s="86">
         <v>0.17780000000000001</v>
       </c>
-      <c r="D14" s="116">
+      <c r="D14" s="87">
         <v>8.2500000000000004E-2</v>
       </c>
-      <c r="E14" s="117"/>
+      <c r="E14" s="136"/>
       <c r="F14" s="50">
         <v>7.9699999999999993E-2</v>
       </c>
       <c r="G14" s="50"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="119">
+      <c r="H14" s="137"/>
+      <c r="I14" s="89">
         <f t="shared" si="1"/>
         <v>0.17236108577029652</v>
       </c>
-      <c r="J14" s="120"/>
-      <c r="K14" s="120"/>
-      <c r="L14" s="120"/>
-      <c r="N14" s="109"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="138"/>
+      <c r="L14" s="138"/>
+      <c r="N14" s="80"/>
       <c r="P14" s="39">
         <f>[2]Consol!$S$51</f>
         <v>842.84570941674997</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A15" s="113"/>
-      <c r="B15" s="114" t="s">
-        <v>326</v>
-      </c>
-      <c r="C15" s="115">
+      <c r="A15" s="135"/>
+      <c r="B15" s="85" t="s">
+        <v>325</v>
+      </c>
+      <c r="C15" s="86">
         <v>2.3300000000000001E-2</v>
       </c>
-      <c r="D15" s="122">
+      <c r="D15" s="91">
         <v>0.06</v>
       </c>
-      <c r="E15" s="117"/>
+      <c r="E15" s="136"/>
       <c r="F15" s="50" t="s">
         <v>132</v>
       </c>
       <c r="G15" s="50"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="119">
+      <c r="H15" s="137"/>
+      <c r="I15" s="89">
         <f t="shared" si="1"/>
         <v>5.5496237804106341E-2</v>
       </c>
-      <c r="J15" s="120"/>
-      <c r="K15" s="120"/>
-      <c r="L15" s="120"/>
-      <c r="M15" s="104"/>
+      <c r="J15" s="138"/>
+      <c r="K15" s="138"/>
+      <c r="L15" s="138"/>
+      <c r="M15" s="75"/>
       <c r="P15" s="39">
         <f>[2]Consol!$S$53</f>
         <v>271.37660286208001</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" s="113"/>
-      <c r="B16" s="114" t="s">
-        <v>327</v>
-      </c>
-      <c r="C16" s="115" t="s">
+      <c r="A16" s="135"/>
+      <c r="B16" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="C16" s="86" t="s">
         <v>132</v>
       </c>
-      <c r="D16" s="116">
+      <c r="D16" s="87">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="E16" s="123" t="s">
+      <c r="E16" s="88" t="s">
         <v>132</v>
       </c>
       <c r="F16" s="50" t="s">
         <v>132</v>
       </c>
       <c r="G16" s="50"/>
-      <c r="H16" s="124" t="s">
-        <v>327</v>
-      </c>
-      <c r="I16" s="119">
+      <c r="H16" s="84" t="s">
+        <v>326</v>
+      </c>
+      <c r="I16" s="89">
         <f t="shared" si="1"/>
         <v>0.18988490239522635</v>
       </c>
-      <c r="J16" s="119">
+      <c r="J16" s="89">
         <f>1100/J4</f>
         <v>0.18676355733641209</v>
       </c>
-      <c r="K16" s="119">
+      <c r="K16" s="89">
         <f>487/K4</f>
         <v>0.15658408758420012</v>
       </c>
-      <c r="L16" s="119" t="s">
+      <c r="L16" s="89" t="s">
         <v>132</v>
       </c>
-      <c r="M16" s="104"/>
+      <c r="M16" s="75"/>
       <c r="P16" s="39">
         <f>[2]Consol!$S$32*[2]Consol!$S$6</f>
         <v>928.5371727126568</v>
       </c>
-      <c r="Q16" s="105">
+      <c r="Q16" s="76">
         <f>P16/5000</f>
         <v>0.18570743454253136</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="113"/>
-      <c r="B17" s="114" t="s">
-        <v>328</v>
-      </c>
-      <c r="C17" s="115">
+      <c r="A17" s="135"/>
+      <c r="B17" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="C17" s="86">
         <v>6.5199999999999994E-2</v>
       </c>
-      <c r="D17" s="125">
+      <c r="D17" s="139">
         <f>840/D4</f>
         <v>0.16561514195583596</v>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="141">
         <f>448/E4</f>
         <v>6.0021436227224008E-2</v>
       </c>
@@ -21576,126 +21585,126 @@
         <v>0.67900000000000005</v>
       </c>
       <c r="G17" s="50"/>
-      <c r="H17" s="124" t="s">
-        <v>329</v>
-      </c>
-      <c r="I17" s="119">
+      <c r="H17" s="84" t="s">
+        <v>328</v>
+      </c>
+      <c r="I17" s="89">
         <f t="shared" si="1"/>
         <v>0.16012269938650306</v>
       </c>
-      <c r="J17" s="119">
+      <c r="J17" s="89">
         <v>0.26400000000000001</v>
       </c>
-      <c r="K17" s="119">
+      <c r="K17" s="89">
         <f>912.55/K4</f>
         <v>0.29341028567753963</v>
       </c>
-      <c r="L17" s="127">
+      <c r="L17" s="93">
         <v>0.26</v>
       </c>
-      <c r="M17" s="128"/>
+      <c r="M17" s="94"/>
       <c r="P17">
         <f>783</f>
         <v>783</v>
       </c>
       <c r="Q17" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A18" s="135"/>
+      <c r="B18" s="85" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A18" s="113"/>
-      <c r="B18" s="114" t="s">
-        <v>331</v>
-      </c>
-      <c r="C18" s="129" t="s">
+      <c r="C18" s="95" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="130"/>
-      <c r="E18" s="126"/>
+      <c r="D18" s="140"/>
+      <c r="E18" s="141"/>
       <c r="F18" s="50">
         <v>3.0800000000000001E-2</v>
       </c>
       <c r="G18" s="50"/>
-      <c r="H18" s="124" t="s">
-        <v>331</v>
-      </c>
-      <c r="I18" s="119">
+      <c r="H18" s="84" t="s">
+        <v>330</v>
+      </c>
+      <c r="I18" s="89">
         <f t="shared" si="1"/>
         <v>6.0531697341513292E-2</v>
       </c>
-      <c r="J18" s="119" t="s">
+      <c r="J18" s="89" t="s">
         <v>132</v>
       </c>
-      <c r="K18" s="119">
+      <c r="K18" s="89">
         <f>45/K4</f>
         <v>1.4468755526260792E-2</v>
       </c>
-      <c r="L18" s="131" t="s">
+      <c r="L18" s="96" t="s">
         <v>132</v>
       </c>
-      <c r="M18" s="128"/>
+      <c r="M18" s="94"/>
       <c r="P18">
         <v>296</v>
       </c>
       <c r="Q18" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="135"/>
+      <c r="B19" s="97" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="113"/>
-      <c r="B19" s="132" t="s">
-        <v>332</v>
-      </c>
-      <c r="C19" s="129">
+      <c r="C19" s="95">
         <v>0.1143</v>
       </c>
-      <c r="D19" s="133">
+      <c r="D19" s="98">
         <f>(1619-840)/D4</f>
         <v>0.15358832807570977</v>
       </c>
-      <c r="E19" s="134">
+      <c r="E19" s="92">
         <f>2269/E4</f>
         <v>0.30399249732047162</v>
       </c>
       <c r="F19" s="50">
         <v>0.1011</v>
       </c>
-      <c r="H19" s="124" t="s">
-        <v>332</v>
-      </c>
-      <c r="I19" s="119">
+      <c r="H19" s="84" t="s">
+        <v>331</v>
+      </c>
+      <c r="I19" s="89">
         <f t="shared" si="1"/>
         <v>0.10777096114519427</v>
       </c>
-      <c r="J19" s="119">
+      <c r="J19" s="89">
         <v>0.19800000000000001</v>
       </c>
-      <c r="K19" s="119">
+      <c r="K19" s="89">
         <f>585.38/K4-K18</f>
         <v>0.17374724691735124</v>
       </c>
-      <c r="L19" s="119">
+      <c r="L19" s="89">
         <v>0.21</v>
       </c>
-      <c r="M19" s="121"/>
+      <c r="M19" s="90"/>
       <c r="P19">
         <f>1606-P17-P18</f>
         <v>527</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A20" s="113"/>
-      <c r="B20" s="114" t="s">
+      <c r="A20" s="135"/>
+      <c r="B20" s="85" t="s">
         <v>208</v>
       </c>
-      <c r="C20" s="115">
+      <c r="C20" s="86">
         <v>6.6100000000000006E-2</v>
       </c>
-      <c r="D20" s="122">
+      <c r="D20" s="91">
         <f>1-SUM(D13:D19)</f>
         <v>4.6296529968454347E-2</v>
       </c>
-      <c r="E20" s="135">
+      <c r="E20" s="99">
         <f>1-SUM(E13:E19)</f>
         <v>0.26898606645230438</v>
       </c>
@@ -21703,22 +21712,22 @@
         <v>7.0900000000000005E-2</v>
       </c>
       <c r="G20" s="50"/>
-      <c r="H20" s="124" t="s">
+      <c r="H20" s="84" t="s">
         <v>208</v>
       </c>
-      <c r="I20" s="136">
+      <c r="I20" s="100">
         <f>1-SUM(I13:I19)</f>
         <v>9.4706380913141763E-2</v>
       </c>
-      <c r="J20" s="119">
+      <c r="J20" s="89">
         <f>1-SUM(J13:J19)</f>
         <v>6.923644266358786E-2</v>
       </c>
-      <c r="K20" s="119">
+      <c r="K20" s="89">
         <f>1-SUM(K13:K19)</f>
         <v>3.6403388904072242E-2</v>
       </c>
-      <c r="L20" s="127">
+      <c r="L20" s="93">
         <v>0.09</v>
       </c>
     </row>
@@ -21735,24 +21744,24 @@
       <c r="M21" s="62"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A22" s="96"/>
-      <c r="B22" s="96"/>
-      <c r="E22" s="105"/>
-      <c r="K22" s="104"/>
+      <c r="A22" s="68"/>
+      <c r="B22" s="68"/>
+      <c r="E22" s="76"/>
+      <c r="K22" s="75"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="C23" s="137"/>
-      <c r="D23" s="137"/>
-      <c r="E23" s="138"/>
-      <c r="F23" s="138"/>
-      <c r="G23" s="138"/>
-      <c r="J23" s="137"/>
-      <c r="K23" s="137"/>
-      <c r="L23" s="137"/>
+      <c r="C23" s="132"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="101"/>
+      <c r="G23" s="101"/>
+      <c r="J23" s="132"/>
+      <c r="K23" s="132"/>
+      <c r="L23" s="132"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A25" s="139"/>
-      <c r="B25" s="140"/>
+      <c r="A25" s="133"/>
+      <c r="B25" s="102"/>
       <c r="C25" s="62"/>
       <c r="D25" s="62"/>
       <c r="E25" s="62"/>
@@ -21761,8 +21770,8 @@
       <c r="I25" s="62"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A26" s="139"/>
-      <c r="B26" s="140"/>
+      <c r="A26" s="133"/>
+      <c r="B26" s="102"/>
       <c r="C26" s="62"/>
       <c r="D26" s="62"/>
       <c r="E26" s="62"/>
@@ -21771,28 +21780,28 @@
       <c r="I26" s="62"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A27" s="139"/>
-      <c r="B27" s="140"/>
+      <c r="A27" s="133"/>
+      <c r="B27" s="102"/>
       <c r="C27" s="62"/>
-      <c r="D27" s="141"/>
+      <c r="D27" s="103"/>
       <c r="E27" s="62"/>
       <c r="F27" s="62"/>
       <c r="G27" s="62"/>
       <c r="I27" s="62"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A28" s="139"/>
-      <c r="B28" s="140"/>
+      <c r="A28" s="133"/>
+      <c r="B28" s="102"/>
       <c r="C28" s="62"/>
-      <c r="D28" s="141"/>
-      <c r="E28" s="141"/>
-      <c r="F28" s="141"/>
-      <c r="G28" s="141"/>
-      <c r="I28" s="141"/>
+      <c r="D28" s="103"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="103"/>
+      <c r="G28" s="103"/>
+      <c r="I28" s="103"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A29" s="139"/>
-      <c r="B29" s="140"/>
+      <c r="A29" s="133"/>
+      <c r="B29" s="102"/>
       <c r="C29" s="62"/>
       <c r="D29" s="62"/>
       <c r="E29" s="62"/>
